--- a/杂项 misc/比较器信号.xlsx
+++ b/杂项 misc/比较器信号.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\杂项 misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1854A1-C62C-44C3-87AB-F84E7BF46C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD6115D-38D6-45E4-A8E8-A06A69ECACE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="容器" sheetId="1" r:id="rId1"/>
-    <sheet name="超限堆叠" sheetId="2" r:id="rId2"/>
-    <sheet name="特殊" sheetId="3" r:id="rId3"/>
+    <sheet name="特殊" sheetId="3" r:id="rId1"/>
+    <sheet name="容器" sheetId="1" r:id="rId2"/>
+    <sheet name="超限堆叠" sheetId="2" r:id="rId3"/>
     <sheet name="唱片" sheetId="4" r:id="rId4"/>
     <sheet name="幽匿感测体" sheetId="6" r:id="rId5"/>
   </sheets>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="244">
   <si>
     <t>容器</t>
   </si>
@@ -126,17 +126,6 @@
     <t>熄灭</t>
   </si>
   <si>
-    <t>最后一次交互槽位(输出1~6)
-(last_interaction_book_slot)
-新放置的输出0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15-floor(15*min(d,32)/32)
-d：嘎枝怪距离其嘎枝之心底面中心的直线距离
-floor()：向下取整
-</t>
-  </si>
-  <si>
     <t>1层堆肥</t>
   </si>
   <si>
@@ -146,9 +135,6 @@
     <t>1等级</t>
   </si>
   <si>
-    <t>未旋转</t>
-  </si>
-  <si>
     <t>吃6片</t>
   </si>
   <si>
@@ -161,9 +147,6 @@
     <t>2等级</t>
   </si>
   <si>
-    <t>旋转1次</t>
-  </si>
-  <si>
     <t>1级</t>
   </si>
   <si>
@@ -179,9 +162,6 @@
     <t>3等级</t>
   </si>
   <si>
-    <t>旋转2次</t>
-  </si>
-  <si>
     <t>吃5片</t>
   </si>
   <si>
@@ -191,45 +171,30 @@
     <t>4等级</t>
   </si>
   <si>
-    <t>旋转3次</t>
-  </si>
-  <si>
     <t>5层堆肥</t>
   </si>
   <si>
     <t>5等级(满)</t>
   </si>
   <si>
-    <t>旋转4次</t>
-  </si>
-  <si>
     <t>吃4片</t>
   </si>
   <si>
     <t>6层堆肥</t>
   </si>
   <si>
-    <t>旋转5次</t>
-  </si>
-  <si>
     <t>2级</t>
   </si>
   <si>
     <t>7层堆肥(过渡)</t>
   </si>
   <si>
-    <t>旋转6次</t>
-  </si>
-  <si>
     <t>吃3片</t>
   </si>
   <si>
     <t>8层堆肥(满)</t>
   </si>
   <si>
-    <t>旋转7次</t>
-  </si>
-  <si>
     <t>吃2片</t>
   </si>
   <si>
@@ -240,9 +205,6 @@
   </si>
   <si>
     <t>完整</t>
-  </si>
-  <si>
-    <t>4级(满)</t>
   </si>
   <si>
     <t>有末影之眼</t>
@@ -682,11 +644,6 @@
   </si>
   <si>
     <t>命令方块</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>有物品占用或被锁定的槽位总数
-也就是非空闲槽位总数</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -702,10 +659,6 @@
   </si>
   <si>
     <t>铜傀儡</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>四种姿势(copper_golem_pose)为“站立(standing)”“坐下(sitting)”“奔跑(running)”“大字(star)”分别输出1~4的信号。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -778,6 +731,129 @@
   </si>
   <si>
     <t>唱片</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>全空</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>信号=可用空槽位总数</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>全新未交互=-1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>最后一次交互槽位
+(last_interaction_book_slot)
+全新未交互的输出0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>■■■=7</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>□■■=6</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>■□■=5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>□□■=4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>■■□=3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>□■□=2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>■□□=1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>站立(standing)=1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>坐下(sitting)=2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>奔跑(running)=3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>大字(star)=4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>四种姿势(copper_golem_pose)分别输出1~4的信号。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>4级</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↗</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>→</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↘</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↓</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↙</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>←</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>↖</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>信号=旋转次数(ItemRotation)+1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>探测铁轨</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">15-floor(15*min(d,32)/32)
+d：嘎枝怪距离其嘎枝之心底面中心的直线距离
+floor()：向下取整
+</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>输出的探测铁轨上命令方块矿车、箱子矿车、漏斗矿车三种矿车的信号
+总是选区与检测范围相交的“第一个”矿车
+检测范围：完整方块除了底面的5个面都向内收缩0.2m所得的形状</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -848,7 +924,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1047,8 +1123,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1097,13 +1203,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1139,218 +1282,257 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="36" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1846,6 +2028,654 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="特殊"/>
+  <dimension ref="A1:AA17"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="5.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="13.77734375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.77734375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="17.33203125" style="3" customWidth="1"/>
+    <col min="15" max="16" width="16.44140625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="19.5546875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="21.21875" style="3" customWidth="1"/>
+    <col min="19" max="19" width="17.33203125" style="3" customWidth="1"/>
+    <col min="20" max="27" width="8.6640625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19">
+      <c r="A1" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="S1" s="12"/>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="18">
+        <v>0</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="77"/>
+      <c r="D2" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="92" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="L2" s="84" t="s">
+        <v>217</v>
+      </c>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="79" t="s">
+        <v>205</v>
+      </c>
+      <c r="P2" s="85" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q2" s="77" t="s">
+        <v>242</v>
+      </c>
+      <c r="R2" s="79" t="s">
+        <v>201</v>
+      </c>
+      <c r="S2" s="78"/>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" s="32">
+        <v>1</v>
+      </c>
+      <c r="B3" s="76"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="77"/>
+      <c r="G3" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="88">
+        <v>1</v>
+      </c>
+      <c r="L3" s="90">
+        <v>1</v>
+      </c>
+      <c r="M3" s="95" t="s">
+        <v>225</v>
+      </c>
+      <c r="N3" s="93" t="s">
+        <v>226</v>
+      </c>
+      <c r="O3" s="79"/>
+      <c r="P3" s="86"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="78"/>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" s="32">
+        <v>2</v>
+      </c>
+      <c r="B4" s="76"/>
+      <c r="C4" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="77"/>
+      <c r="G4" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="41" t="s">
+        <v>233</v>
+      </c>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="88">
+        <v>2</v>
+      </c>
+      <c r="L4" s="90">
+        <v>2</v>
+      </c>
+      <c r="M4" s="95" t="s">
+        <v>224</v>
+      </c>
+      <c r="N4" s="90" t="s">
+        <v>227</v>
+      </c>
+      <c r="O4" s="79"/>
+      <c r="P4" s="86"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="78"/>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" s="32">
+        <v>3</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="44"/>
+      <c r="D5" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="88">
+        <v>3</v>
+      </c>
+      <c r="L5" s="90">
+        <v>3</v>
+      </c>
+      <c r="M5" s="95" t="s">
+        <v>223</v>
+      </c>
+      <c r="N5" s="91" t="s">
+        <v>228</v>
+      </c>
+      <c r="O5" s="79"/>
+      <c r="P5" s="86"/>
+      <c r="Q5" s="77"/>
+      <c r="R5" s="79"/>
+      <c r="S5" s="78"/>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" s="19">
+        <v>4</v>
+      </c>
+      <c r="B6" s="76"/>
+      <c r="C6" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="I6" s="77"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="38">
+        <v>4</v>
+      </c>
+      <c r="L6" s="91">
+        <v>4</v>
+      </c>
+      <c r="M6" s="96" t="s">
+        <v>222</v>
+      </c>
+      <c r="N6" s="94" t="s">
+        <v>229</v>
+      </c>
+      <c r="O6" s="79"/>
+      <c r="P6" s="86"/>
+      <c r="Q6" s="77"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="78"/>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" s="19">
+        <v>5</v>
+      </c>
+      <c r="B7" s="76"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>236</v>
+      </c>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="38">
+        <v>5</v>
+      </c>
+      <c r="L7" s="91">
+        <v>5</v>
+      </c>
+      <c r="M7" s="96" t="s">
+        <v>221</v>
+      </c>
+      <c r="N7" s="85" t="s">
+        <v>230</v>
+      </c>
+      <c r="O7" s="79"/>
+      <c r="P7" s="86"/>
+      <c r="Q7" s="77"/>
+      <c r="R7" s="79"/>
+      <c r="S7" s="78"/>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="20">
+        <v>6</v>
+      </c>
+      <c r="B8" s="76"/>
+      <c r="C8" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="41" t="s">
+        <v>237</v>
+      </c>
+      <c r="I8" s="77"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="38">
+        <v>6</v>
+      </c>
+      <c r="L8" s="91">
+        <v>6</v>
+      </c>
+      <c r="M8" s="96" t="s">
+        <v>220</v>
+      </c>
+      <c r="N8" s="86"/>
+      <c r="O8" s="79"/>
+      <c r="P8" s="86"/>
+      <c r="Q8" s="77"/>
+      <c r="R8" s="79"/>
+      <c r="S8" s="78"/>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="20">
+        <v>7</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="44"/>
+      <c r="D9" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="41" t="s">
+        <v>238</v>
+      </c>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="89">
+        <v>7</v>
+      </c>
+      <c r="L9" s="85" t="s">
+        <v>218</v>
+      </c>
+      <c r="M9" s="96" t="s">
+        <v>219</v>
+      </c>
+      <c r="N9" s="86"/>
+      <c r="O9" s="79"/>
+      <c r="P9" s="86"/>
+      <c r="Q9" s="77"/>
+      <c r="R9" s="79"/>
+      <c r="S9" s="78"/>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" s="21">
+        <v>8</v>
+      </c>
+      <c r="B10" s="76"/>
+      <c r="C10" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="77"/>
+      <c r="H10" s="41" t="s">
+        <v>239</v>
+      </c>
+      <c r="I10" s="77"/>
+      <c r="J10" s="77"/>
+      <c r="K10" s="89">
+        <v>8</v>
+      </c>
+      <c r="L10" s="86"/>
+      <c r="M10" s="85" t="s">
+        <v>202</v>
+      </c>
+      <c r="N10" s="86"/>
+      <c r="O10" s="79"/>
+      <c r="P10" s="86"/>
+      <c r="Q10" s="77"/>
+      <c r="R10" s="79"/>
+      <c r="S10" s="78"/>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" s="22">
+        <v>9</v>
+      </c>
+      <c r="B11" s="76"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77" t="s">
+        <v>240</v>
+      </c>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="89">
+        <v>9</v>
+      </c>
+      <c r="L11" s="86"/>
+      <c r="M11" s="86"/>
+      <c r="N11" s="86"/>
+      <c r="O11" s="79"/>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="77"/>
+      <c r="R11" s="79"/>
+      <c r="S11" s="78"/>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" s="22">
+        <v>10</v>
+      </c>
+      <c r="B12" s="76"/>
+      <c r="C12" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="85" t="s">
+        <v>216</v>
+      </c>
+      <c r="L12" s="86"/>
+      <c r="M12" s="86"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="79"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="77"/>
+      <c r="R12" s="79"/>
+      <c r="S12" s="78"/>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" s="23">
+        <v>11</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="44"/>
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77"/>
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="77"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
+      <c r="M13" s="86"/>
+      <c r="N13" s="86"/>
+      <c r="O13" s="79"/>
+      <c r="P13" s="86"/>
+      <c r="Q13" s="77"/>
+      <c r="R13" s="79"/>
+      <c r="S13" s="78"/>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" s="23">
+        <v>12</v>
+      </c>
+      <c r="B14" s="76"/>
+      <c r="C14" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="77"/>
+      <c r="K14" s="86"/>
+      <c r="L14" s="86"/>
+      <c r="M14" s="86"/>
+      <c r="N14" s="86"/>
+      <c r="O14" s="79"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="77"/>
+      <c r="R14" s="79"/>
+      <c r="S14" s="78"/>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" s="24">
+        <v>13</v>
+      </c>
+      <c r="B15" s="76"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="86"/>
+      <c r="L15" s="86"/>
+      <c r="M15" s="86"/>
+      <c r="N15" s="86"/>
+      <c r="O15" s="79"/>
+      <c r="P15" s="86"/>
+      <c r="Q15" s="77"/>
+      <c r="R15" s="79"/>
+      <c r="S15" s="78"/>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" s="24">
+        <v>14</v>
+      </c>
+      <c r="B16" s="76"/>
+      <c r="C16" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="86"/>
+      <c r="M16" s="86"/>
+      <c r="N16" s="86"/>
+      <c r="O16" s="79"/>
+      <c r="P16" s="86"/>
+      <c r="Q16" s="77"/>
+      <c r="R16" s="79"/>
+      <c r="S16" s="78"/>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" s="26">
+        <v>15</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C17" s="44"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="J17" s="46" t="s">
+        <v>56</v>
+      </c>
+      <c r="K17" s="87"/>
+      <c r="L17" s="87"/>
+      <c r="M17" s="87"/>
+      <c r="N17" s="87"/>
+      <c r="O17" s="79"/>
+      <c r="P17" s="87"/>
+      <c r="Q17" s="77"/>
+      <c r="R17" s="79"/>
+      <c r="S17" s="78"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="Q2:Q17"/>
+    <mergeCell ref="S2:S17"/>
+    <mergeCell ref="R2:R17"/>
+    <mergeCell ref="O2:O17"/>
+    <mergeCell ref="K12:K17"/>
+    <mergeCell ref="L9:L17"/>
+    <mergeCell ref="M10:M17"/>
+    <mergeCell ref="N7:N17"/>
+    <mergeCell ref="P2:P17"/>
+    <mergeCell ref="H11:H17"/>
+    <mergeCell ref="I3:I16"/>
+    <mergeCell ref="J3:J16"/>
+    <mergeCell ref="D11:D17"/>
+    <mergeCell ref="E6:E17"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F6:F17"/>
+    <mergeCell ref="G8:G17"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C2:C3"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="容器"/>
   <dimension ref="A1:AA23"/>
@@ -1864,7 +2694,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -1885,7 +2715,7 @@
       <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="72" t="s">
         <v>0</v>
       </c>
       <c r="J1" s="11" t="s">
@@ -1908,7 +2738,7 @@
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="14"/>
+      <c r="A2" s="75"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
       <c r="D2" s="11" t="s">
@@ -1923,7 +2753,7 @@
       <c r="G2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="18"/>
+      <c r="I2" s="72"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11" t="s">
@@ -1940,7 +2770,7 @@
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="14"/>
+      <c r="A3" s="75"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
@@ -1949,7 +2779,7 @@
         <v>11</v>
       </c>
       <c r="G3" s="11"/>
-      <c r="I3" s="18"/>
+      <c r="I3" s="72"/>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
       <c r="L3" s="11"/>
@@ -1960,14 +2790,14 @@
       <c r="O3" s="11"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="14"/>
+      <c r="A4" s="75"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
-      <c r="I4" s="18"/>
+      <c r="I4" s="72"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
@@ -1976,29 +2806,29 @@
       <c r="O4" s="11"/>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="B5" s="24">
+      <c r="A5" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B5" s="17">
         <v>1</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="17">
         <v>3</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="17">
         <v>5</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="17">
         <v>9</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="17">
         <v>27</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="17">
         <v>54</v>
       </c>
-      <c r="I5" s="23" t="s">
-        <v>223</v>
+      <c r="I5" s="16" t="s">
+        <v>210</v>
       </c>
       <c r="J5" s="10">
         <v>1</v>
@@ -2020,8 +2850,8 @@
       </c>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="23" t="s">
-        <v>224</v>
+      <c r="A6" s="16" t="s">
+        <v>211</v>
       </c>
       <c r="B6" s="5" t="str">
         <f t="shared" ref="B6:G6" si="0">IF(INT(64*B5/14/(9*64))&gt;0,INT(64*B5/14/(9*64))&amp;"行","")&amp;IF(INT(MOD(64*B5/14,(9*64))/64)&gt;0,INT(MOD(64*B5/14,(9*64))/64)&amp;"组","")&amp;IF(ROUND(MOD(64*B5/14,64),1)&gt;0,ROUND(MOD(64*B5/14,64),1)&amp;"个","")</f>
@@ -2047,8 +2877,8 @@
         <f t="shared" si="0"/>
         <v>3组54.9个</v>
       </c>
-      <c r="I6" s="23" t="s">
-        <v>224</v>
+      <c r="I6" s="16" t="s">
+        <v>211</v>
       </c>
       <c r="J6" s="5" t="str">
         <f t="shared" ref="J6:O6" si="1">IF(INT(16*J5/14/(9*16))&gt;0,INT(16*J5/14/(9*16))&amp;"行","")&amp;IF(INT(MOD(16*J5/14,(9*16))/16)&gt;0,INT(MOD(16*J5/14,(9*16))/16)&amp;"组","")&amp;IF(ROUND(MOD(16*J5/14,16),1)&gt;0,ROUND(MOD(16*J5/14,16),1)&amp;"个","")</f>
@@ -2076,858 +2906,858 @@
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="I7" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
+      <c r="A7" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="73" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="I7" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="J7" s="73" t="s">
+        <v>209</v>
+      </c>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="74"/>
+      <c r="O7" s="74"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="21">
+      <c r="A8" s="14">
         <v>0</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="I8" s="21">
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="I8" s="14">
         <v>0</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="K8" s="18"/>
-      <c r="L8" s="18"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="72"/>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="21">
+      <c r="A9" s="14">
         <v>1</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="I9" s="21">
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="I9" s="14">
         <v>1</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="72"/>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="37">
+      <c r="A10" s="30">
         <v>2</v>
       </c>
-      <c r="B10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A10-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A10-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A10-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A10-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A10-1)/14),0),64)&amp;"个","")</f>
+      <c r="B10" s="31" t="str">
+        <f t="shared" ref="B10:G23" si="2">IF(INT(ROUNDUP((64*B$5*($A10-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A10-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A10-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A10-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A10-1)/14),0),64)&amp;"个","")</f>
         <v>5个</v>
       </c>
-      <c r="C10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A10-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A10-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A10-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A10-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A10-1)/14),0),64)&amp;"个","")</f>
+      <c r="C10" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>14个</v>
       </c>
-      <c r="D10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A10-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A10-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A10-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A10-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A10-1)/14),0),64)&amp;"个","")</f>
+      <c r="D10" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>23个</v>
       </c>
-      <c r="E10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A10-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A10-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A10-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A10-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A10-1)/14),0),64)&amp;"个","")</f>
+      <c r="E10" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>42个</v>
       </c>
-      <c r="F10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A10-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A10-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A10-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A10-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A10-1)/14),0),64)&amp;"个","")</f>
+      <c r="F10" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>1组60个</v>
       </c>
-      <c r="G10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A10-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A10-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A10-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A10-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A10-1)/14),0),64)&amp;"个","")</f>
+      <c r="G10" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>3组55个</v>
       </c>
-      <c r="I10" s="37">
+      <c r="I10" s="30">
         <v>2</v>
       </c>
-      <c r="J10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A10-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A10-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A10-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A10-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A10-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A10-1)/14),0),16)&amp;"个","")</f>
+      <c r="J10" s="31" t="str">
+        <f t="shared" ref="J10:O23" si="3">IF(INT(ROUNDUP((16*J$5*($A10-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A10-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A10-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A10-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A10-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A10-1)/14),0),16)&amp;"个","")</f>
         <v>2个</v>
       </c>
-      <c r="K10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A10-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A10-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A10-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A10-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A10-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A10-1)/14),0),16)&amp;"个","")</f>
+      <c r="K10" s="31" t="str">
+        <f t="shared" si="3"/>
         <v>4个</v>
       </c>
-      <c r="L10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A10-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A10-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A10-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A10-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A10-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A10-1)/14),0),16)&amp;"个","")</f>
+      <c r="L10" s="31" t="str">
+        <f t="shared" si="3"/>
         <v>6个</v>
       </c>
-      <c r="M10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A10-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A10-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A10-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A10-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A10-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A10-1)/14),0),16)&amp;"个","")</f>
+      <c r="M10" s="31" t="str">
+        <f t="shared" si="3"/>
         <v>11个</v>
       </c>
-      <c r="N10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A10-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A10-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A10-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A10-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A10-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A10-1)/14),0),16)&amp;"个","")</f>
+      <c r="N10" s="31" t="str">
+        <f t="shared" si="3"/>
         <v>1组15个</v>
       </c>
-      <c r="O10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A10-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A10-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A10-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A10-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A10-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A10-1)/14),0),16)&amp;"个","")</f>
+      <c r="O10" s="31" t="str">
+        <f t="shared" si="3"/>
         <v>3组14个</v>
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="37">
+      <c r="A11" s="30">
         <v>3</v>
       </c>
-      <c r="B11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A11-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A11-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A11-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A11-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A11-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A11-1)/14),0),64)&amp;"个","")</f>
+      <c r="B11" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>10个</v>
       </c>
-      <c r="C11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A11-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A11-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A11-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A11-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A11-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A11-1)/14),0),64)&amp;"个","")</f>
+      <c r="C11" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>28个</v>
       </c>
-      <c r="D11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A11-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A11-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A11-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A11-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A11-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A11-1)/14),0),64)&amp;"个","")</f>
+      <c r="D11" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>46个</v>
       </c>
-      <c r="E11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A11-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A11-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A11-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A11-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A11-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A11-1)/14),0),64)&amp;"个","")</f>
+      <c r="E11" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>1组19个</v>
       </c>
-      <c r="F11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A11-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A11-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A11-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A11-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A11-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A11-1)/14),0),64)&amp;"个","")</f>
+      <c r="F11" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>3组55个</v>
       </c>
-      <c r="G11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A11-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A11-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A11-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A11-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A11-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A11-1)/14),0),64)&amp;"个","")</f>
+      <c r="G11" s="31" t="str">
+        <f t="shared" si="2"/>
         <v>7组46个</v>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="30">
         <v>3</v>
       </c>
-      <c r="J11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A11-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A11-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A11-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A11-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A11-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A11-1)/14),0),16)&amp;"个","")</f>
+      <c r="J11" s="31" t="str">
+        <f t="shared" si="3"/>
         <v>3个</v>
       </c>
-      <c r="K11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A11-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A11-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A11-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A11-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A11-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A11-1)/14),0),16)&amp;"个","")</f>
+      <c r="K11" s="31" t="str">
+        <f t="shared" si="3"/>
         <v>7个</v>
       </c>
-      <c r="L11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A11-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A11-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A11-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A11-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A11-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A11-1)/14),0),16)&amp;"个","")</f>
+      <c r="L11" s="31" t="str">
+        <f t="shared" si="3"/>
         <v>12个</v>
       </c>
-      <c r="M11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A11-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A11-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A11-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A11-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A11-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A11-1)/14),0),16)&amp;"个","")</f>
+      <c r="M11" s="31" t="str">
+        <f t="shared" si="3"/>
         <v>1组5个</v>
       </c>
-      <c r="N11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A11-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A11-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A11-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A11-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A11-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A11-1)/14),0),16)&amp;"个","")</f>
+      <c r="N11" s="31" t="str">
+        <f t="shared" si="3"/>
         <v>3组14个</v>
       </c>
-      <c r="O11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A11-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A11-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A11-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A11-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A11-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A11-1)/14),0),16)&amp;"个","")</f>
+      <c r="O11" s="31" t="str">
+        <f t="shared" si="3"/>
         <v>7组12个</v>
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="26">
+      <c r="A12" s="19">
         <v>4</v>
       </c>
-      <c r="B12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A12-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A12-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A12-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A12-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A12-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A12-1)/14),0),64)&amp;"个","")</f>
+      <c r="B12" s="19" t="str">
+        <f t="shared" si="2"/>
         <v>14个</v>
       </c>
-      <c r="C12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A12-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A12-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A12-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A12-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A12-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A12-1)/14),0),64)&amp;"个","")</f>
+      <c r="C12" s="19" t="str">
+        <f t="shared" si="2"/>
         <v>42个</v>
       </c>
-      <c r="D12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A12-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A12-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A12-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A12-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A12-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A12-1)/14),0),64)&amp;"个","")</f>
+      <c r="D12" s="19" t="str">
+        <f t="shared" si="2"/>
         <v>1组5个</v>
       </c>
-      <c r="E12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A12-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A12-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A12-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A12-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A12-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A12-1)/14),0),64)&amp;"个","")</f>
+      <c r="E12" s="19" t="str">
+        <f t="shared" si="2"/>
         <v>1组60个</v>
       </c>
-      <c r="F12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A12-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A12-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A12-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A12-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A12-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A12-1)/14),0),64)&amp;"个","")</f>
+      <c r="F12" s="19" t="str">
+        <f t="shared" si="2"/>
         <v>5组51个</v>
       </c>
-      <c r="G12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A12-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A12-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A12-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A12-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A12-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A12-1)/14),0),64)&amp;"个","")</f>
+      <c r="G12" s="19" t="str">
+        <f t="shared" si="2"/>
         <v>1行2组37个</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="19">
         <v>4</v>
       </c>
-      <c r="J12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A12-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A12-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A12-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A12-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A12-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A12-1)/14),0),16)&amp;"个","")</f>
+      <c r="J12" s="19" t="str">
+        <f t="shared" si="3"/>
         <v>4个</v>
       </c>
-      <c r="K12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A12-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A12-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A12-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A12-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A12-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A12-1)/14),0),16)&amp;"个","")</f>
+      <c r="K12" s="19" t="str">
+        <f t="shared" si="3"/>
         <v>11个</v>
       </c>
-      <c r="L12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A12-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A12-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A12-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A12-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A12-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A12-1)/14),0),16)&amp;"个","")</f>
+      <c r="L12" s="19" t="str">
+        <f t="shared" si="3"/>
         <v>1组2个</v>
       </c>
-      <c r="M12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A12-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A12-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A12-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A12-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A12-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A12-1)/14),0),16)&amp;"个","")</f>
+      <c r="M12" s="19" t="str">
+        <f t="shared" si="3"/>
         <v>1组15个</v>
       </c>
-      <c r="N12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A12-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A12-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A12-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A12-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A12-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A12-1)/14),0),16)&amp;"个","")</f>
+      <c r="N12" s="19" t="str">
+        <f t="shared" si="3"/>
         <v>5组13个</v>
       </c>
-      <c r="O12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A12-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A12-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A12-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A12-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A12-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A12-1)/14),0),16)&amp;"个","")</f>
+      <c r="O12" s="19" t="str">
+        <f t="shared" si="3"/>
         <v>1行2组10个</v>
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="26">
+      <c r="A13" s="19">
         <v>5</v>
       </c>
-      <c r="B13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A13-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A13-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A13-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A13-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A13-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A13-1)/14),0),64)&amp;"个","")</f>
+      <c r="B13" s="19" t="str">
+        <f t="shared" si="2"/>
         <v>19个</v>
       </c>
-      <c r="C13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A13-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A13-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A13-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A13-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A13-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A13-1)/14),0),64)&amp;"个","")</f>
+      <c r="C13" s="19" t="str">
+        <f t="shared" si="2"/>
         <v>55个</v>
       </c>
-      <c r="D13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A13-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A13-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A13-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A13-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A13-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A13-1)/14),0),64)&amp;"个","")</f>
+      <c r="D13" s="19" t="str">
+        <f t="shared" si="2"/>
         <v>1组28个</v>
       </c>
-      <c r="E13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A13-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A13-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A13-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A13-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A13-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A13-1)/14),0),64)&amp;"个","")</f>
+      <c r="E13" s="19" t="str">
+        <f t="shared" si="2"/>
         <v>2组37个</v>
       </c>
-      <c r="F13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A13-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A13-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A13-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A13-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A13-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A13-1)/14),0),64)&amp;"个","")</f>
+      <c r="F13" s="19" t="str">
+        <f t="shared" si="2"/>
         <v>7组46个</v>
       </c>
-      <c r="G13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A13-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A13-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A13-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A13-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A13-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A13-1)/14),0),64)&amp;"个","")</f>
+      <c r="G13" s="19" t="str">
+        <f t="shared" si="2"/>
         <v>1行6组28个</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="19">
         <v>5</v>
       </c>
-      <c r="J13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A13-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A13-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A13-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A13-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A13-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A13-1)/14),0),16)&amp;"个","")</f>
+      <c r="J13" s="19" t="str">
+        <f t="shared" si="3"/>
         <v>5个</v>
       </c>
-      <c r="K13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A13-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A13-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A13-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A13-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A13-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A13-1)/14),0),16)&amp;"个","")</f>
+      <c r="K13" s="19" t="str">
+        <f t="shared" si="3"/>
         <v>14个</v>
       </c>
-      <c r="L13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A13-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A13-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A13-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A13-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A13-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A13-1)/14),0),16)&amp;"个","")</f>
+      <c r="L13" s="19" t="str">
+        <f t="shared" si="3"/>
         <v>1组7个</v>
       </c>
-      <c r="M13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A13-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A13-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A13-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A13-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A13-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A13-1)/14),0),16)&amp;"个","")</f>
+      <c r="M13" s="19" t="str">
+        <f t="shared" si="3"/>
         <v>2组10个</v>
       </c>
-      <c r="N13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A13-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A13-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A13-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A13-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A13-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A13-1)/14),0),16)&amp;"个","")</f>
+      <c r="N13" s="19" t="str">
+        <f t="shared" si="3"/>
         <v>7组12个</v>
       </c>
-      <c r="O13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A13-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A13-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A13-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A13-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A13-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A13-1)/14),0),16)&amp;"个","")</f>
+      <c r="O13" s="19" t="str">
+        <f t="shared" si="3"/>
         <v>1行6组7个</v>
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="27">
+      <c r="A14" s="20">
         <v>6</v>
       </c>
-      <c r="B14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A14-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A14-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A14-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A14-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A14-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A14-1)/14),0),64)&amp;"个","")</f>
+      <c r="B14" s="20" t="str">
+        <f t="shared" si="2"/>
         <v>23个</v>
       </c>
-      <c r="C14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A14-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A14-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A14-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A14-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A14-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A14-1)/14),0),64)&amp;"个","")</f>
+      <c r="C14" s="20" t="str">
+        <f t="shared" si="2"/>
         <v>1组5个</v>
       </c>
-      <c r="D14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A14-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A14-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A14-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A14-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A14-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A14-1)/14),0),64)&amp;"个","")</f>
+      <c r="D14" s="20" t="str">
+        <f t="shared" si="2"/>
         <v>1组51个</v>
       </c>
-      <c r="E14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A14-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A14-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A14-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A14-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A14-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A14-1)/14),0),64)&amp;"个","")</f>
+      <c r="E14" s="20" t="str">
+        <f t="shared" si="2"/>
         <v>3组14个</v>
       </c>
-      <c r="F14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A14-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A14-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A14-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A14-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A14-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A14-1)/14),0),64)&amp;"个","")</f>
+      <c r="F14" s="20" t="str">
+        <f t="shared" si="2"/>
         <v>1行42个</v>
       </c>
-      <c r="G14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A14-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A14-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A14-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A14-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A14-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A14-1)/14),0),64)&amp;"个","")</f>
+      <c r="G14" s="20" t="str">
+        <f t="shared" si="2"/>
         <v>2行1组19个</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="20">
         <v>6</v>
       </c>
-      <c r="J14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A14-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A14-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A14-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A14-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A14-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A14-1)/14),0),16)&amp;"个","")</f>
+      <c r="J14" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>6个</v>
       </c>
-      <c r="K14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A14-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A14-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A14-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A14-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A14-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A14-1)/14),0),16)&amp;"个","")</f>
+      <c r="K14" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>1组2个</v>
       </c>
-      <c r="L14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A14-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A14-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A14-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A14-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A14-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A14-1)/14),0),16)&amp;"个","")</f>
+      <c r="L14" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>1组13个</v>
       </c>
-      <c r="M14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A14-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A14-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A14-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A14-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A14-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A14-1)/14),0),16)&amp;"个","")</f>
+      <c r="M14" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>3组4个</v>
       </c>
-      <c r="N14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A14-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A14-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A14-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A14-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A14-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A14-1)/14),0),16)&amp;"个","")</f>
+      <c r="N14" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>1行11个</v>
       </c>
-      <c r="O14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A14-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A14-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A14-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A14-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A14-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A14-1)/14),0),16)&amp;"个","")</f>
+      <c r="O14" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>2行1组5个</v>
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="27">
+      <c r="A15" s="20">
         <v>7</v>
       </c>
-      <c r="B15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A15-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A15-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A15-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A15-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A15-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A15-1)/14),0),64)&amp;"个","")</f>
+      <c r="B15" s="20" t="str">
+        <f t="shared" si="2"/>
         <v>28个</v>
       </c>
-      <c r="C15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A15-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A15-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A15-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A15-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A15-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A15-1)/14),0),64)&amp;"个","")</f>
+      <c r="C15" s="20" t="str">
+        <f t="shared" si="2"/>
         <v>1组19个</v>
       </c>
-      <c r="D15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A15-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A15-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A15-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A15-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A15-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A15-1)/14),0),64)&amp;"个","")</f>
+      <c r="D15" s="20" t="str">
+        <f t="shared" si="2"/>
         <v>2组10个</v>
       </c>
-      <c r="E15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A15-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A15-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A15-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A15-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A15-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A15-1)/14),0),64)&amp;"个","")</f>
+      <c r="E15" s="20" t="str">
+        <f t="shared" si="2"/>
         <v>3组55个</v>
       </c>
-      <c r="F15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A15-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A15-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A15-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A15-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A15-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A15-1)/14),0),64)&amp;"个","")</f>
+      <c r="F15" s="20" t="str">
+        <f t="shared" si="2"/>
         <v>1行2组37个</v>
       </c>
-      <c r="G15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A15-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A15-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A15-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A15-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A15-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A15-1)/14),0),64)&amp;"个","")</f>
+      <c r="G15" s="20" t="str">
+        <f t="shared" si="2"/>
         <v>2行5组10个</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="20">
         <v>7</v>
       </c>
-      <c r="J15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A15-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A15-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A15-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A15-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A15-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A15-1)/14),0),16)&amp;"个","")</f>
+      <c r="J15" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>7个</v>
       </c>
-      <c r="K15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A15-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A15-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A15-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A15-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A15-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A15-1)/14),0),16)&amp;"个","")</f>
+      <c r="K15" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>1组5个</v>
       </c>
-      <c r="L15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A15-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A15-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A15-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A15-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A15-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A15-1)/14),0),16)&amp;"个","")</f>
+      <c r="L15" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>2组3个</v>
       </c>
-      <c r="M15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A15-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A15-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A15-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A15-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A15-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A15-1)/14),0),16)&amp;"个","")</f>
+      <c r="M15" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>3组14个</v>
       </c>
-      <c r="N15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A15-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A15-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A15-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A15-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A15-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A15-1)/14),0),16)&amp;"个","")</f>
+      <c r="N15" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>1行2组10个</v>
       </c>
-      <c r="O15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A15-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A15-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A15-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A15-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A15-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A15-1)/14),0),16)&amp;"个","")</f>
+      <c r="O15" s="20" t="str">
+        <f t="shared" si="3"/>
         <v>2行5组3个</v>
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="34">
+      <c r="A16" s="27">
         <v>8</v>
       </c>
-      <c r="B16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A16-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A16-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A16-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A16-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A16-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A16-1)/14),0),64)&amp;"个","")</f>
+      <c r="B16" s="27" t="str">
+        <f t="shared" si="2"/>
         <v>32个</v>
       </c>
-      <c r="C16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A16-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A16-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A16-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A16-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A16-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A16-1)/14),0),64)&amp;"个","")</f>
+      <c r="C16" s="27" t="str">
+        <f t="shared" si="2"/>
         <v>1组32个</v>
       </c>
-      <c r="D16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A16-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A16-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A16-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A16-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A16-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A16-1)/14),0),64)&amp;"个","")</f>
+      <c r="D16" s="27" t="str">
+        <f t="shared" si="2"/>
         <v>2组32个</v>
       </c>
-      <c r="E16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A16-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A16-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A16-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A16-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A16-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A16-1)/14),0),64)&amp;"个","")</f>
+      <c r="E16" s="27" t="str">
+        <f t="shared" si="2"/>
         <v>4组32个</v>
       </c>
-      <c r="F16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A16-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A16-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A16-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A16-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A16-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A16-1)/14),0),64)&amp;"个","")</f>
+      <c r="F16" s="27" t="str">
+        <f t="shared" si="2"/>
         <v>1行4组32个</v>
       </c>
-      <c r="G16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A16-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A16-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A16-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A16-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A16-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A16-1)/14),0),64)&amp;"个","")</f>
+      <c r="G16" s="27" t="str">
+        <f t="shared" si="2"/>
         <v>3行</v>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="27">
         <v>8</v>
       </c>
-      <c r="J16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A16-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A16-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A16-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A16-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A16-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A16-1)/14),0),16)&amp;"个","")</f>
+      <c r="J16" s="27" t="str">
+        <f t="shared" si="3"/>
         <v>8个</v>
       </c>
-      <c r="K16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A16-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A16-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A16-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A16-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A16-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A16-1)/14),0),16)&amp;"个","")</f>
+      <c r="K16" s="27" t="str">
+        <f t="shared" si="3"/>
         <v>1组8个</v>
       </c>
-      <c r="L16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A16-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A16-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A16-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A16-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A16-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A16-1)/14),0),16)&amp;"个","")</f>
+      <c r="L16" s="27" t="str">
+        <f t="shared" si="3"/>
         <v>2组8个</v>
       </c>
-      <c r="M16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A16-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A16-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A16-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A16-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A16-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A16-1)/14),0),16)&amp;"个","")</f>
+      <c r="M16" s="27" t="str">
+        <f t="shared" si="3"/>
         <v>4组8个</v>
       </c>
-      <c r="N16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A16-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A16-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A16-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A16-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A16-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A16-1)/14),0),16)&amp;"个","")</f>
+      <c r="N16" s="27" t="str">
+        <f t="shared" si="3"/>
         <v>1行4组8个</v>
       </c>
-      <c r="O16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A16-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A16-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A16-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A16-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A16-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A16-1)/14),0),16)&amp;"个","")</f>
+      <c r="O16" s="27" t="str">
+        <f t="shared" si="3"/>
         <v>3行</v>
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="29">
+      <c r="A17" s="22">
         <v>9</v>
       </c>
-      <c r="B17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A17-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A17-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A17-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A17-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A17-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A17-1)/14),0),64)&amp;"个","")</f>
+      <c r="B17" s="22" t="str">
+        <f t="shared" si="2"/>
         <v>37个</v>
       </c>
-      <c r="C17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A17-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A17-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A17-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A17-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A17-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A17-1)/14),0),64)&amp;"个","")</f>
+      <c r="C17" s="22" t="str">
+        <f t="shared" si="2"/>
         <v>1组46个</v>
       </c>
-      <c r="D17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A17-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A17-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A17-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A17-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A17-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A17-1)/14),0),64)&amp;"个","")</f>
+      <c r="D17" s="22" t="str">
+        <f t="shared" si="2"/>
         <v>2组55个</v>
       </c>
-      <c r="E17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A17-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A17-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A17-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A17-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A17-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A17-1)/14),0),64)&amp;"个","")</f>
+      <c r="E17" s="22" t="str">
+        <f t="shared" si="2"/>
         <v>5组10个</v>
       </c>
-      <c r="F17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A17-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A17-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A17-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A17-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A17-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A17-1)/14),0),64)&amp;"个","")</f>
+      <c r="F17" s="22" t="str">
+        <f t="shared" si="2"/>
         <v>1行6组28个</v>
       </c>
-      <c r="G17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A17-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A17-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A17-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A17-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A17-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A17-1)/14),0),64)&amp;"个","")</f>
+      <c r="G17" s="22" t="str">
+        <f t="shared" si="2"/>
         <v>3行3组55个</v>
       </c>
-      <c r="I17" s="29">
+      <c r="I17" s="22">
         <v>9</v>
       </c>
-      <c r="J17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A17-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A17-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A17-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A17-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A17-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A17-1)/14),0),16)&amp;"个","")</f>
+      <c r="J17" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>10个</v>
       </c>
-      <c r="K17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A17-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A17-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A17-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A17-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A17-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A17-1)/14),0),16)&amp;"个","")</f>
+      <c r="K17" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>1组12个</v>
       </c>
-      <c r="L17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A17-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A17-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A17-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A17-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A17-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A17-1)/14),0),16)&amp;"个","")</f>
+      <c r="L17" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>2组14个</v>
       </c>
-      <c r="M17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A17-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A17-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A17-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A17-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A17-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A17-1)/14),0),16)&amp;"个","")</f>
+      <c r="M17" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>5组3个</v>
       </c>
-      <c r="N17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A17-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A17-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A17-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A17-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A17-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A17-1)/14),0),16)&amp;"个","")</f>
+      <c r="N17" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>1行6组7个</v>
       </c>
-      <c r="O17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A17-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A17-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A17-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A17-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A17-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A17-1)/14),0),16)&amp;"个","")</f>
+      <c r="O17" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>3行3组14个</v>
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="29">
+      <c r="A18" s="22">
         <v>10</v>
       </c>
-      <c r="B18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A18-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A18-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A18-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A18-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A18-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A18-1)/14),0),64)&amp;"个","")</f>
+      <c r="B18" s="22" t="str">
+        <f t="shared" si="2"/>
         <v>42个</v>
       </c>
-      <c r="C18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A18-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A18-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A18-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A18-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A18-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A18-1)/14),0),64)&amp;"个","")</f>
+      <c r="C18" s="22" t="str">
+        <f t="shared" si="2"/>
         <v>1组60个</v>
       </c>
-      <c r="D18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A18-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A18-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A18-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A18-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A18-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A18-1)/14),0),64)&amp;"个","")</f>
+      <c r="D18" s="22" t="str">
+        <f t="shared" si="2"/>
         <v>3组14个</v>
       </c>
-      <c r="E18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A18-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A18-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A18-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A18-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A18-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A18-1)/14),0),64)&amp;"个","")</f>
+      <c r="E18" s="22" t="str">
+        <f t="shared" si="2"/>
         <v>5组51个</v>
       </c>
-      <c r="F18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A18-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A18-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A18-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A18-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A18-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A18-1)/14),0),64)&amp;"个","")</f>
+      <c r="F18" s="22" t="str">
+        <f t="shared" si="2"/>
         <v>1行8组23个</v>
       </c>
-      <c r="G18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A18-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A18-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A18-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A18-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A18-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A18-1)/14),0),64)&amp;"个","")</f>
+      <c r="G18" s="22" t="str">
+        <f t="shared" si="2"/>
         <v>3行7组46个</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="22">
         <v>10</v>
       </c>
-      <c r="J18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A18-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A18-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A18-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A18-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A18-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A18-1)/14),0),16)&amp;"个","")</f>
+      <c r="J18" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>11个</v>
       </c>
-      <c r="K18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A18-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A18-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A18-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A18-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A18-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A18-1)/14),0),16)&amp;"个","")</f>
+      <c r="K18" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>1组15个</v>
       </c>
-      <c r="L18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A18-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A18-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A18-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A18-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A18-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A18-1)/14),0),16)&amp;"个","")</f>
+      <c r="L18" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>3组4个</v>
       </c>
-      <c r="M18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A18-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A18-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A18-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A18-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A18-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A18-1)/14),0),16)&amp;"个","")</f>
+      <c r="M18" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>5组13个</v>
       </c>
-      <c r="N18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A18-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A18-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A18-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A18-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A18-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A18-1)/14),0),16)&amp;"个","")</f>
+      <c r="N18" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>1行8组6个</v>
       </c>
-      <c r="O18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A18-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A18-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A18-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A18-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A18-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A18-1)/14),0),16)&amp;"个","")</f>
+      <c r="O18" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>3行7组12个</v>
       </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="30">
+      <c r="A19" s="23">
         <v>11</v>
       </c>
-      <c r="B19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A19-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A19-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A19-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A19-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A19-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A19-1)/14),0),64)&amp;"个","")</f>
+      <c r="B19" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>46个</v>
       </c>
-      <c r="C19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A19-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A19-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A19-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A19-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A19-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A19-1)/14),0),64)&amp;"个","")</f>
+      <c r="C19" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>2组10个</v>
       </c>
-      <c r="D19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A19-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A19-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A19-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A19-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A19-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A19-1)/14),0),64)&amp;"个","")</f>
+      <c r="D19" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>3组37个</v>
       </c>
-      <c r="E19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A19-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A19-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A19-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A19-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A19-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A19-1)/14),0),64)&amp;"个","")</f>
+      <c r="E19" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>6组28个</v>
       </c>
-      <c r="F19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A19-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A19-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A19-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A19-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A19-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A19-1)/14),0),64)&amp;"个","")</f>
+      <c r="F19" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>2行1组19个</v>
       </c>
-      <c r="G19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A19-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A19-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A19-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A19-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A19-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A19-1)/14),0),64)&amp;"个","")</f>
+      <c r="G19" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>4行2组37个</v>
       </c>
-      <c r="I19" s="30">
+      <c r="I19" s="23">
         <v>11</v>
       </c>
-      <c r="J19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A19-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A19-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A19-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A19-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A19-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A19-1)/14),0),16)&amp;"个","")</f>
+      <c r="J19" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>12个</v>
       </c>
-      <c r="K19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A19-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A19-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A19-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A19-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A19-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A19-1)/14),0),16)&amp;"个","")</f>
+      <c r="K19" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>2组3个</v>
       </c>
-      <c r="L19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A19-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A19-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A19-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A19-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A19-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A19-1)/14),0),16)&amp;"个","")</f>
+      <c r="L19" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>3组10个</v>
       </c>
-      <c r="M19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A19-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A19-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A19-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A19-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A19-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A19-1)/14),0),16)&amp;"个","")</f>
+      <c r="M19" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>6组7个</v>
       </c>
-      <c r="N19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A19-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A19-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A19-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A19-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A19-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A19-1)/14),0),16)&amp;"个","")</f>
+      <c r="N19" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>2行1组5个</v>
       </c>
-      <c r="O19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A19-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A19-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A19-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A19-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A19-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A19-1)/14),0),16)&amp;"个","")</f>
+      <c r="O19" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>4行2组10个</v>
       </c>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="30">
+      <c r="A20" s="23">
         <v>12</v>
       </c>
-      <c r="B20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A20-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A20-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A20-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A20-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A20-1)/14),0),64)&amp;"个","")</f>
+      <c r="B20" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>51个</v>
       </c>
-      <c r="C20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A20-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A20-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A20-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A20-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A20-1)/14),0),64)&amp;"个","")</f>
+      <c r="C20" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>2组23个</v>
       </c>
-      <c r="D20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A20-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A20-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A20-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A20-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A20-1)/14),0),64)&amp;"个","")</f>
+      <c r="D20" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>3组60个</v>
       </c>
-      <c r="E20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A20-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A20-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A20-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A20-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A20-1)/14),0),64)&amp;"个","")</f>
+      <c r="E20" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>7组5个</v>
       </c>
-      <c r="F20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A20-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A20-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A20-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A20-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A20-1)/14),0),64)&amp;"个","")</f>
+      <c r="F20" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>2行3组14个</v>
       </c>
-      <c r="G20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A20-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A20-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A20-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A20-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A20-1)/14),0),64)&amp;"个","")</f>
+      <c r="G20" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>4行6组28个</v>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="23">
         <v>12</v>
       </c>
-      <c r="J20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A20-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A20-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A20-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A20-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A20-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A20-1)/14),0),16)&amp;"个","")</f>
+      <c r="J20" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>13个</v>
       </c>
-      <c r="K20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A20-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A20-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A20-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A20-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A20-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A20-1)/14),0),16)&amp;"个","")</f>
+      <c r="K20" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>2组6个</v>
       </c>
-      <c r="L20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A20-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A20-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A20-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A20-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A20-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A20-1)/14),0),16)&amp;"个","")</f>
+      <c r="L20" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>3组15个</v>
       </c>
-      <c r="M20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A20-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A20-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A20-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A20-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A20-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A20-1)/14),0),16)&amp;"个","")</f>
+      <c r="M20" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>7组2个</v>
       </c>
-      <c r="N20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A20-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A20-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A20-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A20-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A20-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A20-1)/14),0),16)&amp;"个","")</f>
+      <c r="N20" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>2行3组4个</v>
       </c>
-      <c r="O20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A20-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A20-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A20-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A20-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A20-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A20-1)/14),0),16)&amp;"个","")</f>
+      <c r="O20" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>4行6组7个</v>
       </c>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="31">
+      <c r="A21" s="24">
         <v>13</v>
       </c>
-      <c r="B21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A21-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A21-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A21-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A21-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A21-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A21-1)/14),0),64)&amp;"个","")</f>
+      <c r="B21" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>55个</v>
       </c>
-      <c r="C21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A21-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A21-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A21-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A21-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A21-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A21-1)/14),0),64)&amp;"个","")</f>
+      <c r="C21" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>2组37个</v>
       </c>
-      <c r="D21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A21-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A21-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A21-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A21-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A21-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A21-1)/14),0),64)&amp;"个","")</f>
+      <c r="D21" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>4组19个</v>
       </c>
-      <c r="E21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A21-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A21-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A21-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A21-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A21-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A21-1)/14),0),64)&amp;"个","")</f>
+      <c r="E21" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>7组46个</v>
       </c>
-      <c r="F21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A21-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A21-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A21-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A21-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A21-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A21-1)/14),0),64)&amp;"个","")</f>
+      <c r="F21" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>2行5组10个</v>
       </c>
-      <c r="G21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A21-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A21-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A21-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A21-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A21-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A21-1)/14),0),64)&amp;"个","")</f>
+      <c r="G21" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>5行1组19个</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="24">
         <v>13</v>
       </c>
-      <c r="J21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A21-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A21-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A21-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A21-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A21-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A21-1)/14),0),16)&amp;"个","")</f>
+      <c r="J21" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>14个</v>
       </c>
-      <c r="K21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A21-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A21-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A21-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A21-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A21-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A21-1)/14),0),16)&amp;"个","")</f>
+      <c r="K21" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>2组10个</v>
       </c>
-      <c r="L21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A21-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A21-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A21-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A21-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A21-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A21-1)/14),0),16)&amp;"个","")</f>
+      <c r="L21" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>4组5个</v>
       </c>
-      <c r="M21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A21-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A21-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A21-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A21-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A21-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A21-1)/14),0),16)&amp;"个","")</f>
+      <c r="M21" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>7组12个</v>
       </c>
-      <c r="N21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A21-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A21-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A21-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A21-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A21-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A21-1)/14),0),16)&amp;"个","")</f>
+      <c r="N21" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>2行5组3个</v>
       </c>
-      <c r="O21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A21-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A21-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A21-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A21-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A21-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A21-1)/14),0),16)&amp;"个","")</f>
+      <c r="O21" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>5行1组5个</v>
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="31">
+      <c r="A22" s="24">
         <v>14</v>
       </c>
-      <c r="B22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A22-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A22-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A22-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A22-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A22-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A22-1)/14),0),64)&amp;"个","")</f>
+      <c r="B22" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>60个</v>
       </c>
-      <c r="C22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A22-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A22-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A22-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A22-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A22-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A22-1)/14),0),64)&amp;"个","")</f>
+      <c r="C22" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>2组51个</v>
       </c>
-      <c r="D22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A22-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A22-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A22-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A22-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A22-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A22-1)/14),0),64)&amp;"个","")</f>
+      <c r="D22" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>4组42个</v>
       </c>
-      <c r="E22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A22-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A22-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A22-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A22-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A22-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A22-1)/14),0),64)&amp;"个","")</f>
+      <c r="E22" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>8组23个</v>
       </c>
-      <c r="F22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A22-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A22-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A22-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A22-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A22-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A22-1)/14),0),64)&amp;"个","")</f>
+      <c r="F22" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>2行7组5个</v>
       </c>
-      <c r="G22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A22-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A22-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A22-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A22-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A22-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A22-1)/14),0),64)&amp;"个","")</f>
+      <c r="G22" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>5行5组10个</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="24">
         <v>14</v>
       </c>
-      <c r="J22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A22-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A22-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A22-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A22-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A22-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A22-1)/14),0),16)&amp;"个","")</f>
+      <c r="J22" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>15个</v>
       </c>
-      <c r="K22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A22-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A22-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A22-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A22-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A22-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A22-1)/14),0),16)&amp;"个","")</f>
+      <c r="K22" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>2组13个</v>
       </c>
-      <c r="L22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A22-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A22-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A22-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A22-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A22-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A22-1)/14),0),16)&amp;"个","")</f>
+      <c r="L22" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>4组11个</v>
       </c>
-      <c r="M22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A22-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A22-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A22-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A22-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A22-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A22-1)/14),0),16)&amp;"个","")</f>
+      <c r="M22" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>8组6个</v>
       </c>
-      <c r="N22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A22-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A22-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A22-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A22-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A22-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A22-1)/14),0),16)&amp;"个","")</f>
+      <c r="N22" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>2行7组2个</v>
       </c>
-      <c r="O22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A22-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A22-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A22-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A22-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A22-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A22-1)/14),0),16)&amp;"个","")</f>
+      <c r="O22" s="25" t="str">
+        <f t="shared" si="3"/>
         <v>5行5组3个</v>
       </c>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="35">
+      <c r="A23" s="28">
         <v>15</v>
       </c>
-      <c r="B23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A23-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*B$5*($A23-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A23-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A23-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*B$5*($A23-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A23-1)/14),0),64)&amp;"个","")</f>
+      <c r="B23" s="29" t="str">
+        <f t="shared" si="2"/>
         <v>1组</v>
       </c>
-      <c r="C23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A23-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*C$5*($A23-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A23-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A23-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*C$5*($A23-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A23-1)/14),0),64)&amp;"个","")</f>
+      <c r="C23" s="29" t="str">
+        <f t="shared" si="2"/>
         <v>3组</v>
       </c>
-      <c r="D23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A23-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*D$5*($A23-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A23-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A23-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*D$5*($A23-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A23-1)/14),0),64)&amp;"个","")</f>
+      <c r="D23" s="29" t="str">
+        <f t="shared" si="2"/>
         <v>5组</v>
       </c>
-      <c r="E23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A23-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*E$5*($A23-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A23-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A23-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*E$5*($A23-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A23-1)/14),0),64)&amp;"个","")</f>
+      <c r="E23" s="29" t="str">
+        <f t="shared" si="2"/>
         <v>1行</v>
       </c>
-      <c r="F23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A23-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*F$5*($A23-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A23-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A23-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*F$5*($A23-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A23-1)/14),0),64)&amp;"个","")</f>
+      <c r="F23" s="29" t="str">
+        <f t="shared" si="2"/>
         <v>3行</v>
       </c>
-      <c r="G23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A23-1)/14),0)/(9*64))&gt;0,INT(ROUNDUP((64*G$5*($A23-1)/14),0)/(9*64))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A23-1)/14),0),(9*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A23-1)/14),0),(9*64))/64)&amp;"组","")&amp;IF(MOD(ROUNDUP((64*G$5*($A23-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A23-1)/14),0),64)&amp;"个","")</f>
+      <c r="G23" s="29" t="str">
+        <f t="shared" si="2"/>
         <v>6行</v>
       </c>
-      <c r="I23" s="35">
+      <c r="I23" s="28">
         <v>15</v>
       </c>
-      <c r="J23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((16*J$5*($A23-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*J$5*($A23-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*J$5*($A23-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*J$5*($A23-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*J$5*($A23-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*J$5*($A23-1)/14),0),16)&amp;"个","")</f>
+      <c r="J23" s="29" t="str">
+        <f t="shared" si="3"/>
         <v>1组</v>
       </c>
-      <c r="K23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((16*K$5*($A23-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*K$5*($A23-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*K$5*($A23-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*K$5*($A23-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*K$5*($A23-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*K$5*($A23-1)/14),0),16)&amp;"个","")</f>
+      <c r="K23" s="29" t="str">
+        <f t="shared" si="3"/>
         <v>3组</v>
       </c>
-      <c r="L23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((16*L$5*($A23-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*L$5*($A23-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*L$5*($A23-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*L$5*($A23-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*L$5*($A23-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*L$5*($A23-1)/14),0),16)&amp;"个","")</f>
+      <c r="L23" s="29" t="str">
+        <f t="shared" si="3"/>
         <v>5组</v>
       </c>
-      <c r="M23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((16*M$5*($A23-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*M$5*($A23-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*M$5*($A23-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*M$5*($A23-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*M$5*($A23-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*M$5*($A23-1)/14),0),16)&amp;"个","")</f>
+      <c r="M23" s="29" t="str">
+        <f t="shared" si="3"/>
         <v>1行</v>
       </c>
-      <c r="N23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((16*N$5*($A23-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*N$5*($A23-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*N$5*($A23-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*N$5*($A23-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*N$5*($A23-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*N$5*($A23-1)/14),0),16)&amp;"个","")</f>
+      <c r="N23" s="29" t="str">
+        <f t="shared" si="3"/>
         <v>3行</v>
       </c>
-      <c r="O23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((16*O$5*($A23-1)/14),0)/(9*16))&gt;0,INT(ROUNDUP((16*O$5*($A23-1)/14),0)/(9*16))&amp;"行","")&amp;IF(INT(MOD(ROUNDUP((16*O$5*($A23-1)/14),0),(9*16))/16)&gt;0,INT(MOD(ROUNDUP((16*O$5*($A23-1)/14),0),(9*16))/16)&amp;"组","")&amp;IF(MOD(ROUNDUP((16*O$5*($A23-1)/14),0),16)&gt;0,MOD(ROUNDUP((16*O$5*($A23-1)/14),0),16)&amp;"个","")</f>
+      <c r="O23" s="29" t="str">
+        <f t="shared" si="3"/>
         <v>6行</v>
       </c>
     </row>
@@ -2947,7 +3777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="超限堆叠"/>
   <dimension ref="A1:G26"/>
@@ -2961,7 +3791,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -2984,7 +3814,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14"/>
+      <c r="A2" s="75"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
       <c r="D2" s="11" t="s">
@@ -3001,7 +3831,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="14"/>
+      <c r="A3" s="75"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
@@ -3012,7 +3842,7 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="14"/>
+      <c r="A4" s="75"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
@@ -3022,7 +3852,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="10" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="B5" s="10">
         <v>1</v>
@@ -3045,7 +3875,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="10" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="B6" s="5" t="str">
         <f t="shared" ref="B6:G6" si="0">IF(INT(64*B5/14/(9*64))&gt;0,INT(64*B5/14/(9*64))&amp;"行","")&amp;IF(INT(MOD(64*B5/14,(9*64))/64)&gt;0,INT(MOD(64*B5/14,(9*64))/64)&amp;"组","")&amp;IF(ROUND(MOD(64*B5/14,64),1)&gt;0,ROUND(MOD(64*B5/14,64),1)&amp;"个","")</f>
@@ -3074,475 +3904,475 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+        <v>207</v>
+      </c>
+      <c r="B7" s="73" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="21">
+      <c r="A8" s="14">
         <v>0</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="21">
+      <c r="A9" s="14">
         <v>1</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="37">
+      <c r="A10" s="30">
         <v>2</v>
       </c>
-      <c r="B10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A10-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A10-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A10-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A10-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A10-1)/14),0),64)&amp;"个","")</f>
+      <c r="B10" s="31" t="str">
+        <f t="shared" ref="B10:G19" si="1">IF(INT(ROUNDUP((64*B$5*($A10-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A10-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A10-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A10-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A10-1)/14),0),64)&amp;"个","")</f>
         <v>5个</v>
       </c>
-      <c r="C10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A10-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A10-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A10-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A10-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A10-1)/14),0),64)&amp;"个","")</f>
+      <c r="C10" s="31" t="str">
+        <f t="shared" si="1"/>
         <v>14个</v>
       </c>
-      <c r="D10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A10-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A10-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A10-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A10-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A10-1)/14),0),64)&amp;"个","")</f>
+      <c r="D10" s="31" t="str">
+        <f t="shared" si="1"/>
         <v>23个</v>
       </c>
-      <c r="E10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A10-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A10-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A10-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A10-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A10-1)/14),0),64)&amp;"个","")</f>
+      <c r="E10" s="31" t="str">
+        <f t="shared" si="1"/>
         <v>42个</v>
       </c>
-      <c r="F10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A10-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A10-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A10-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A10-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A10-1)/14),0),64)&amp;"个","")</f>
+      <c r="F10" s="31" t="str">
+        <f t="shared" si="1"/>
         <v>1叠60个</v>
       </c>
-      <c r="G10" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A10-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A10-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A10-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A10-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A10-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A10-1)/14),0),64)&amp;"个","")</f>
+      <c r="G10" s="31" t="str">
+        <f t="shared" si="1"/>
         <v>3叠55个</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="37">
+      <c r="A11" s="30">
         <v>3</v>
       </c>
-      <c r="B11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A11-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A11-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A11-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A11-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A11-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A11-1)/14),0),64)&amp;"个","")</f>
+      <c r="B11" s="31" t="str">
+        <f t="shared" si="1"/>
         <v>10个</v>
       </c>
-      <c r="C11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A11-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A11-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A11-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A11-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A11-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A11-1)/14),0),64)&amp;"个","")</f>
+      <c r="C11" s="31" t="str">
+        <f t="shared" si="1"/>
         <v>28个</v>
       </c>
-      <c r="D11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A11-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A11-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A11-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A11-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A11-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A11-1)/14),0),64)&amp;"个","")</f>
+      <c r="D11" s="31" t="str">
+        <f t="shared" si="1"/>
         <v>46个</v>
       </c>
-      <c r="E11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A11-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A11-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A11-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A11-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A11-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A11-1)/14),0),64)&amp;"个","")</f>
+      <c r="E11" s="31" t="str">
+        <f t="shared" si="1"/>
         <v>1叠19个</v>
       </c>
-      <c r="F11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A11-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A11-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A11-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A11-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A11-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A11-1)/14),0),64)&amp;"个","")</f>
+      <c r="F11" s="31" t="str">
+        <f t="shared" si="1"/>
         <v>3叠55个</v>
       </c>
-      <c r="G11" s="38" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A11-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A11-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A11-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A11-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A11-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A11-1)/14),0),64)&amp;"个","")</f>
+      <c r="G11" s="31" t="str">
+        <f t="shared" si="1"/>
         <v>7叠46个</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="26">
+      <c r="A12" s="19">
         <v>4</v>
       </c>
-      <c r="B12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A12-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A12-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A12-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A12-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A12-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A12-1)/14),0),64)&amp;"个","")</f>
+      <c r="B12" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>14个</v>
       </c>
-      <c r="C12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A12-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A12-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A12-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A12-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A12-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A12-1)/14),0),64)&amp;"个","")</f>
+      <c r="C12" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>42个</v>
       </c>
-      <c r="D12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A12-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A12-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A12-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A12-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A12-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A12-1)/14),0),64)&amp;"个","")</f>
+      <c r="D12" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>1叠5个</v>
       </c>
-      <c r="E12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A12-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A12-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A12-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A12-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A12-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A12-1)/14),0),64)&amp;"个","")</f>
+      <c r="E12" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>1叠60个</v>
       </c>
-      <c r="F12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A12-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A12-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A12-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A12-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A12-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A12-1)/14),0),64)&amp;"个","")</f>
+      <c r="F12" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>5叠51个</v>
       </c>
-      <c r="G12" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A12-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A12-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A12-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A12-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A12-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A12-1)/14),0),64)&amp;"个","")</f>
+      <c r="G12" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>11叠37个</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="26">
+      <c r="A13" s="19">
         <v>5</v>
       </c>
-      <c r="B13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A13-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A13-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A13-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A13-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A13-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A13-1)/14),0),64)&amp;"个","")</f>
+      <c r="B13" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>19个</v>
       </c>
-      <c r="C13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A13-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A13-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A13-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A13-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A13-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A13-1)/14),0),64)&amp;"个","")</f>
+      <c r="C13" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>55个</v>
       </c>
-      <c r="D13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A13-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A13-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A13-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A13-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A13-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A13-1)/14),0),64)&amp;"个","")</f>
+      <c r="D13" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>1叠28个</v>
       </c>
-      <c r="E13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A13-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A13-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A13-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A13-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A13-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A13-1)/14),0),64)&amp;"个","")</f>
+      <c r="E13" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>2叠37个</v>
       </c>
-      <c r="F13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A13-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A13-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A13-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A13-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A13-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A13-1)/14),0),64)&amp;"个","")</f>
+      <c r="F13" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>7叠46个</v>
       </c>
-      <c r="G13" s="26" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A13-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A13-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A13-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A13-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A13-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A13-1)/14),0),64)&amp;"个","")</f>
+      <c r="G13" s="19" t="str">
+        <f t="shared" si="1"/>
         <v>15叠28个</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="27">
+      <c r="A14" s="20">
         <v>6</v>
       </c>
-      <c r="B14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A14-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A14-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A14-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A14-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A14-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A14-1)/14),0),64)&amp;"个","")</f>
+      <c r="B14" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>23个</v>
       </c>
-      <c r="C14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A14-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A14-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A14-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A14-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A14-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A14-1)/14),0),64)&amp;"个","")</f>
+      <c r="C14" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>1叠5个</v>
       </c>
-      <c r="D14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A14-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A14-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A14-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A14-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A14-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A14-1)/14),0),64)&amp;"个","")</f>
+      <c r="D14" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>1叠51个</v>
       </c>
-      <c r="E14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A14-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A14-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A14-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A14-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A14-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A14-1)/14),0),64)&amp;"个","")</f>
+      <c r="E14" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>3叠14个</v>
       </c>
-      <c r="F14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A14-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A14-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A14-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A14-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A14-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A14-1)/14),0),64)&amp;"个","")</f>
+      <c r="F14" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>9叠42个</v>
       </c>
-      <c r="G14" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A14-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A14-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A14-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A14-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A14-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A14-1)/14),0),64)&amp;"个","")</f>
+      <c r="G14" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>19叠19个</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="27">
+      <c r="A15" s="20">
         <v>7</v>
       </c>
-      <c r="B15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A15-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A15-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A15-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A15-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A15-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A15-1)/14),0),64)&amp;"个","")</f>
+      <c r="B15" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>28个</v>
       </c>
-      <c r="C15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A15-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A15-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A15-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A15-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A15-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A15-1)/14),0),64)&amp;"个","")</f>
+      <c r="C15" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>1叠19个</v>
       </c>
-      <c r="D15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A15-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A15-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A15-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A15-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A15-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A15-1)/14),0),64)&amp;"个","")</f>
+      <c r="D15" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>2叠10个</v>
       </c>
-      <c r="E15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A15-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A15-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A15-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A15-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A15-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A15-1)/14),0),64)&amp;"个","")</f>
+      <c r="E15" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>3叠55个</v>
       </c>
-      <c r="F15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A15-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A15-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A15-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A15-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A15-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A15-1)/14),0),64)&amp;"个","")</f>
+      <c r="F15" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>11叠37个</v>
       </c>
-      <c r="G15" s="27" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A15-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A15-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A15-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A15-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A15-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A15-1)/14),0),64)&amp;"个","")</f>
+      <c r="G15" s="20" t="str">
+        <f t="shared" si="1"/>
         <v>23叠10个</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="34">
+      <c r="A16" s="27">
         <v>8</v>
       </c>
-      <c r="B16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A16-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A16-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A16-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A16-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A16-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A16-1)/14),0),64)&amp;"个","")</f>
+      <c r="B16" s="27" t="str">
+        <f t="shared" si="1"/>
         <v>32个</v>
       </c>
-      <c r="C16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A16-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A16-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A16-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A16-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A16-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A16-1)/14),0),64)&amp;"个","")</f>
+      <c r="C16" s="27" t="str">
+        <f t="shared" si="1"/>
         <v>1叠32个</v>
       </c>
-      <c r="D16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A16-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A16-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A16-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A16-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A16-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A16-1)/14),0),64)&amp;"个","")</f>
+      <c r="D16" s="27" t="str">
+        <f t="shared" si="1"/>
         <v>2叠32个</v>
       </c>
-      <c r="E16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A16-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A16-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A16-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A16-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A16-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A16-1)/14),0),64)&amp;"个","")</f>
+      <c r="E16" s="27" t="str">
+        <f t="shared" si="1"/>
         <v>4叠32个</v>
       </c>
-      <c r="F16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A16-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A16-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A16-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A16-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A16-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A16-1)/14),0),64)&amp;"个","")</f>
+      <c r="F16" s="27" t="str">
+        <f t="shared" si="1"/>
         <v>13叠32个</v>
       </c>
-      <c r="G16" s="34" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A16-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A16-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A16-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A16-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A16-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A16-1)/14),0),64)&amp;"个","")</f>
+      <c r="G16" s="27" t="str">
+        <f t="shared" si="1"/>
         <v>27叠</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="29">
+      <c r="A17" s="22">
         <v>9</v>
       </c>
-      <c r="B17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A17-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A17-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A17-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A17-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A17-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A17-1)/14),0),64)&amp;"个","")</f>
+      <c r="B17" s="22" t="str">
+        <f t="shared" si="1"/>
         <v>37个</v>
       </c>
-      <c r="C17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A17-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A17-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A17-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A17-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A17-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A17-1)/14),0),64)&amp;"个","")</f>
+      <c r="C17" s="22" t="str">
+        <f t="shared" si="1"/>
         <v>1叠46个</v>
       </c>
-      <c r="D17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A17-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A17-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A17-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A17-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A17-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A17-1)/14),0),64)&amp;"个","")</f>
+      <c r="D17" s="22" t="str">
+        <f t="shared" si="1"/>
         <v>2叠55个</v>
       </c>
-      <c r="E17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A17-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A17-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A17-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A17-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A17-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A17-1)/14),0),64)&amp;"个","")</f>
+      <c r="E17" s="22" t="str">
+        <f t="shared" si="1"/>
         <v>5叠10个</v>
       </c>
-      <c r="F17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A17-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A17-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A17-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A17-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A17-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A17-1)/14),0),64)&amp;"个","")</f>
+      <c r="F17" s="22" t="str">
+        <f t="shared" si="1"/>
         <v>15叠28个</v>
       </c>
-      <c r="G17" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A17-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A17-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A17-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A17-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A17-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A17-1)/14),0),64)&amp;"个","")</f>
+      <c r="G17" s="22" t="str">
+        <f t="shared" si="1"/>
         <v>30叠55个</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="29">
+      <c r="A18" s="22">
         <v>10</v>
       </c>
-      <c r="B18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A18-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A18-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A18-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A18-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A18-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A18-1)/14),0),64)&amp;"个","")</f>
+      <c r="B18" s="22" t="str">
+        <f t="shared" si="1"/>
         <v>42个</v>
       </c>
-      <c r="C18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A18-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A18-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A18-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A18-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A18-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A18-1)/14),0),64)&amp;"个","")</f>
+      <c r="C18" s="22" t="str">
+        <f t="shared" si="1"/>
         <v>1叠60个</v>
       </c>
-      <c r="D18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A18-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A18-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A18-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A18-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A18-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A18-1)/14),0),64)&amp;"个","")</f>
+      <c r="D18" s="22" t="str">
+        <f t="shared" si="1"/>
         <v>3叠14个</v>
       </c>
-      <c r="E18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A18-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A18-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A18-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A18-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A18-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A18-1)/14),0),64)&amp;"个","")</f>
+      <c r="E18" s="22" t="str">
+        <f t="shared" si="1"/>
         <v>5叠51个</v>
       </c>
-      <c r="F18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A18-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A18-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A18-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A18-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A18-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A18-1)/14),0),64)&amp;"个","")</f>
+      <c r="F18" s="22" t="str">
+        <f t="shared" si="1"/>
         <v>17叠23个</v>
       </c>
-      <c r="G18" s="29" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A18-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A18-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A18-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A18-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A18-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A18-1)/14),0),64)&amp;"个","")</f>
+      <c r="G18" s="22" t="str">
+        <f t="shared" si="1"/>
         <v>34叠46个</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="30">
+      <c r="A19" s="23">
         <v>11</v>
       </c>
-      <c r="B19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A19-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A19-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A19-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A19-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A19-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A19-1)/14),0),64)&amp;"个","")</f>
+      <c r="B19" s="23" t="str">
+        <f t="shared" si="1"/>
         <v>46个</v>
       </c>
-      <c r="C19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A19-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A19-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A19-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A19-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A19-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A19-1)/14),0),64)&amp;"个","")</f>
+      <c r="C19" s="23" t="str">
+        <f t="shared" si="1"/>
         <v>2叠10个</v>
       </c>
-      <c r="D19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A19-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A19-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A19-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A19-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A19-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A19-1)/14),0),64)&amp;"个","")</f>
+      <c r="D19" s="23" t="str">
+        <f t="shared" si="1"/>
         <v>3叠37个</v>
       </c>
-      <c r="E19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A19-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A19-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A19-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A19-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A19-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A19-1)/14),0),64)&amp;"个","")</f>
+      <c r="E19" s="23" t="str">
+        <f t="shared" si="1"/>
         <v>6叠28个</v>
       </c>
-      <c r="F19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A19-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A19-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A19-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A19-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A19-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A19-1)/14),0),64)&amp;"个","")</f>
+      <c r="F19" s="23" t="str">
+        <f t="shared" si="1"/>
         <v>19叠19个</v>
       </c>
-      <c r="G19" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A19-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A19-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A19-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A19-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A19-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A19-1)/14),0),64)&amp;"个","")</f>
+      <c r="G19" s="23" t="str">
+        <f t="shared" si="1"/>
         <v>38叠37个</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="30">
+      <c r="A20" s="23">
         <v>12</v>
       </c>
-      <c r="B20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A20-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A20-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A20-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A20-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A20-1)/14),0),64)&amp;"个","")</f>
+      <c r="B20" s="23" t="str">
+        <f t="shared" ref="B20:G26" si="2">IF(INT(ROUNDUP((64*B$5*($A20-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A20-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A20-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A20-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A20-1)/14),0),64)&amp;"个","")</f>
         <v>51个</v>
       </c>
-      <c r="C20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A20-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A20-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A20-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A20-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A20-1)/14),0),64)&amp;"个","")</f>
+      <c r="C20" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>2叠23个</v>
       </c>
-      <c r="D20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A20-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A20-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A20-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A20-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A20-1)/14),0),64)&amp;"个","")</f>
+      <c r="D20" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>3叠60个</v>
       </c>
-      <c r="E20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A20-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A20-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A20-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A20-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A20-1)/14),0),64)&amp;"个","")</f>
+      <c r="E20" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>7叠5个</v>
       </c>
-      <c r="F20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A20-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A20-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A20-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A20-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A20-1)/14),0),64)&amp;"个","")</f>
+      <c r="F20" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>21叠14个</v>
       </c>
-      <c r="G20" s="30" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A20-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A20-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A20-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A20-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A20-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A20-1)/14),0),64)&amp;"个","")</f>
+      <c r="G20" s="23" t="str">
+        <f t="shared" si="2"/>
         <v>42叠28个</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="31">
+      <c r="A21" s="24">
         <v>13</v>
       </c>
-      <c r="B21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A21-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A21-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A21-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A21-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A21-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A21-1)/14),0),64)&amp;"个","")</f>
+      <c r="B21" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>55个</v>
       </c>
-      <c r="C21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A21-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A21-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A21-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A21-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A21-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A21-1)/14),0),64)&amp;"个","")</f>
+      <c r="C21" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>2叠37个</v>
       </c>
-      <c r="D21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A21-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A21-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A21-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A21-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A21-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A21-1)/14),0),64)&amp;"个","")</f>
+      <c r="D21" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>4叠19个</v>
       </c>
-      <c r="E21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A21-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A21-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A21-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A21-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A21-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A21-1)/14),0),64)&amp;"个","")</f>
+      <c r="E21" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>7叠46个</v>
       </c>
-      <c r="F21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A21-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A21-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A21-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A21-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A21-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A21-1)/14),0),64)&amp;"个","")</f>
+      <c r="F21" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>23叠10个</v>
       </c>
-      <c r="G21" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A21-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A21-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A21-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A21-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A21-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A21-1)/14),0),64)&amp;"个","")</f>
+      <c r="G21" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>46叠19个</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="31">
+      <c r="A22" s="24">
         <v>14</v>
       </c>
-      <c r="B22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A22-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A22-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A22-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A22-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A22-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A22-1)/14),0),64)&amp;"个","")</f>
+      <c r="B22" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>60个</v>
       </c>
-      <c r="C22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A22-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A22-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A22-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A22-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A22-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A22-1)/14),0),64)&amp;"个","")</f>
+      <c r="C22" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>2叠51个</v>
       </c>
-      <c r="D22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A22-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A22-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A22-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A22-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A22-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A22-1)/14),0),64)&amp;"个","")</f>
+      <c r="D22" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>4叠42个</v>
       </c>
-      <c r="E22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A22-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A22-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A22-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A22-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A22-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A22-1)/14),0),64)&amp;"个","")</f>
+      <c r="E22" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>8叠23个</v>
       </c>
-      <c r="F22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A22-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A22-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A22-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A22-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A22-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A22-1)/14),0),64)&amp;"个","")</f>
+      <c r="F22" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>25叠5个</v>
       </c>
-      <c r="G22" s="32" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A22-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A22-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A22-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A22-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A22-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A22-1)/14),0),64)&amp;"个","")</f>
+      <c r="G22" s="25" t="str">
+        <f t="shared" si="2"/>
         <v>50叠10个</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="35">
+      <c r="A23" s="28">
         <v>15</v>
       </c>
-      <c r="B23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A23-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A23-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A23-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A23-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A23-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A23-1)/14),0),64)&amp;"个","")</f>
+      <c r="B23" s="29" t="str">
+        <f t="shared" si="2"/>
         <v>1叠</v>
       </c>
-      <c r="C23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A23-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A23-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A23-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A23-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A23-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A23-1)/14),0),64)&amp;"个","")</f>
+      <c r="C23" s="29" t="str">
+        <f t="shared" si="2"/>
         <v>3叠</v>
       </c>
-      <c r="D23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A23-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A23-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A23-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A23-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A23-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A23-1)/14),0),64)&amp;"个","")</f>
+      <c r="D23" s="29" t="str">
+        <f t="shared" si="2"/>
         <v>5叠</v>
       </c>
-      <c r="E23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A23-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A23-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A23-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A23-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A23-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A23-1)/14),0),64)&amp;"个","")</f>
+      <c r="E23" s="29" t="str">
+        <f t="shared" si="2"/>
         <v>9叠</v>
       </c>
-      <c r="F23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A23-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A23-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A23-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A23-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A23-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A23-1)/14),0),64)&amp;"个","")</f>
+      <c r="F23" s="29" t="str">
+        <f t="shared" si="2"/>
         <v>27叠</v>
       </c>
-      <c r="G23" s="36" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A23-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A23-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A23-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A23-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A23-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A23-1)/14),0),64)&amp;"个","")</f>
+      <c r="G23" s="29" t="str">
+        <f t="shared" si="2"/>
         <v>54叠</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="16">
+      <c r="A24" s="13">
         <v>16</v>
       </c>
       <c r="B24" s="6" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A24-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A24-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A24-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A24-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A24-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A24-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>1叠5个</v>
       </c>
       <c r="C24" s="6" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A24-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A24-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A24-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A24-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A24-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A24-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>3叠14个</v>
       </c>
       <c r="D24" s="6" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A24-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A24-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A24-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A24-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A24-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A24-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>5叠23个</v>
       </c>
       <c r="E24" s="6" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A24-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A24-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A24-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A24-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A24-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A24-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>9叠42个</v>
       </c>
       <c r="F24" s="6" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A24-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A24-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A24-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A24-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A24-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A24-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>28叠60个</v>
       </c>
       <c r="G24" s="6" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A24-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A24-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A24-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A24-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A24-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A24-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>57叠55个</v>
       </c>
     </row>
@@ -3551,27 +4381,27 @@
         <v>225</v>
       </c>
       <c r="B25" s="6" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A25-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A25-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A25-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A25-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A25-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A25-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>16叠</v>
       </c>
       <c r="C25" s="6" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A25-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A25-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A25-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A25-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A25-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A25-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>48叠</v>
       </c>
       <c r="D25" s="6" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A25-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A25-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A25-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A25-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A25-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A25-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>1满叠16叠</v>
       </c>
       <c r="E25" s="6" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A25-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A25-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A25-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A25-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A25-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A25-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>2满叠16叠</v>
       </c>
       <c r="F25" s="6" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A25-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A25-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A25-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A25-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A25-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A25-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>6满叠48叠</v>
       </c>
       <c r="G25" s="6" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A25-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A25-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A25-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A25-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A25-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A25-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>13满叠32叠</v>
       </c>
     </row>
@@ -3580,27 +4410,27 @@
         <v>897</v>
       </c>
       <c r="B26" s="8" t="str">
-        <f>IF(INT(ROUNDUP((64*B$5*($A26-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*B$5*($A26-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*B$5*($A26-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*B$5*($A26-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*B$5*($A26-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*B$5*($A26-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>1满叠</v>
       </c>
       <c r="C26" s="8" t="str">
-        <f>IF(INT(ROUNDUP((64*C$5*($A26-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*C$5*($A26-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*C$5*($A26-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*C$5*($A26-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*C$5*($A26-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*C$5*($A26-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>3满叠</v>
       </c>
       <c r="D26" s="8" t="str">
-        <f>IF(INT(ROUNDUP((64*D$5*($A26-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*D$5*($A26-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*D$5*($A26-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*D$5*($A26-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*D$5*($A26-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*D$5*($A26-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>5满叠</v>
       </c>
       <c r="E26" s="8" t="str">
-        <f>IF(INT(ROUNDUP((64*E$5*($A26-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*E$5*($A26-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*E$5*($A26-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*E$5*($A26-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*E$5*($A26-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*E$5*($A26-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>9满叠</v>
       </c>
       <c r="F26" s="8" t="str">
-        <f>IF(INT(ROUNDUP((64*F$5*($A26-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*F$5*($A26-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*F$5*($A26-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*F$5*($A26-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*F$5*($A26-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*F$5*($A26-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>27满叠</v>
       </c>
       <c r="G26" s="8" t="str">
-        <f>IF(INT(ROUNDUP((64*G$5*($A26-1)/14),0)/(64*64))&gt;0,INT(ROUNDUP((64*G$5*($A26-1)/14),0)/(64*64))&amp;"满叠","")&amp;IF(INT(MOD(ROUNDUP((64*G$5*($A26-1)/14),0),(64*64))/64)&gt;0,INT(MOD(ROUNDUP((64*G$5*($A26-1)/14),0),(64*64))/64)&amp;"叠","")&amp;IF(MOD(ROUNDUP((64*G$5*($A26-1)/14),0),64)&gt;0,MOD(ROUNDUP((64*G$5*($A26-1)/14),0),64)&amp;"个","")</f>
+        <f t="shared" si="2"/>
         <v>54满叠</v>
       </c>
     </row>
@@ -3610,573 +4440,6 @@
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="B8:G8"/>
     <mergeCell ref="B9:G9"/>
-  </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr codeName="特殊"/>
-  <dimension ref="A1:Z17"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8"/>
-  <cols>
-    <col min="1" max="1" width="7.88671875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="7.77734375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="5.21875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="11.109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12" style="3" customWidth="1"/>
-    <col min="9" max="9" width="15" style="3" customWidth="1"/>
-    <col min="10" max="10" width="7.44140625" style="3" customWidth="1"/>
-    <col min="11" max="12" width="16.44140625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="20.77734375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="23.109375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="25.44140625" style="3" customWidth="1"/>
-    <col min="16" max="16" width="15.6640625" style="3" customWidth="1"/>
-    <col min="17" max="17" width="14.109375" style="3" customWidth="1"/>
-    <col min="18" max="18" width="17.33203125" style="3" customWidth="1"/>
-    <col min="19" max="26" width="8.6640625" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18">
-      <c r="A1" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="M1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="O1" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="P1" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q1" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="R1" s="12"/>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="25">
-        <v>0</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="L2" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="M2" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="N2" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q2" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="R2" s="15"/>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="39">
-        <v>1</v>
-      </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="49" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="15"/>
-    </row>
-    <row r="4" spans="1:18" ht="27.6">
-      <c r="A4" s="39">
-        <v>2</v>
-      </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="15"/>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="39">
-        <v>3</v>
-      </c>
-      <c r="B5" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="52"/>
-      <c r="D5" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="54" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="H5" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="15"/>
-    </row>
-    <row r="6" spans="1:18" ht="27.6">
-      <c r="A6" s="26">
-        <v>4</v>
-      </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="55" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="15"/>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="26">
-        <v>5</v>
-      </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="55" t="s">
-        <v>49</v>
-      </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="15"/>
-    </row>
-    <row r="8" spans="1:18" ht="27.6">
-      <c r="A8" s="27">
-        <v>6</v>
-      </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="55" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="49" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="15"/>
-    </row>
-    <row r="9" spans="1:18" ht="27.6">
-      <c r="A9" s="27">
-        <v>7</v>
-      </c>
-      <c r="B9" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="15"/>
-    </row>
-    <row r="10" spans="1:18" ht="27.6">
-      <c r="A10" s="28">
-        <v>8</v>
-      </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="49" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="15"/>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="29">
-        <v>9</v>
-      </c>
-      <c r="B11" s="46"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="15"/>
-    </row>
-    <row r="12" spans="1:18" ht="27.6">
-      <c r="A12" s="29">
-        <v>10</v>
-      </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="15"/>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="30">
-        <v>11</v>
-      </c>
-      <c r="B13" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="20"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="15"/>
-    </row>
-    <row r="14" spans="1:18" ht="27.6">
-      <c r="A14" s="30">
-        <v>12</v>
-      </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="58" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="15"/>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="31">
-        <v>13</v>
-      </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="15"/>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="31">
-        <v>14</v>
-      </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="56" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="15"/>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" s="33">
-        <v>15</v>
-      </c>
-      <c r="B17" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="61" t="s">
-        <v>66</v>
-      </c>
-      <c r="J17" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="15"/>
-    </row>
-  </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D11:D17"/>
-    <mergeCell ref="E6:E17"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F6:F17"/>
-    <mergeCell ref="G8:G17"/>
-    <mergeCell ref="H11:H17"/>
-    <mergeCell ref="I3:I16"/>
-    <mergeCell ref="J3:J16"/>
-    <mergeCell ref="M2:M17"/>
-    <mergeCell ref="N2:N17"/>
-    <mergeCell ref="O2:O17"/>
-    <mergeCell ref="P2:P17"/>
-    <mergeCell ref="Q2:Q17"/>
-    <mergeCell ref="R2:R17"/>
-    <mergeCell ref="K2:K17"/>
-    <mergeCell ref="L2:L17"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4196,24 +4459,24 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="B1" s="83" t="s">
-        <v>227</v>
-      </c>
-      <c r="C1" s="82"/>
+        <v>207</v>
+      </c>
+      <c r="B1" s="82" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1" s="83"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="25">
+      <c r="A2" s="18">
         <v>0</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C2" s="81"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="39">
+      <c r="A3" s="32">
         <v>1</v>
       </c>
       <c r="B3" s="4">
@@ -4222,141 +4485,141 @@
       <c r="C3" s="4"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="39">
+      <c r="A4" s="32">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C4" s="4"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="39">
+      <c r="A5" s="32">
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C5" s="4"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="26">
+      <c r="A6" s="19">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="26">
+      <c r="A7" s="19">
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="27">
+      <c r="A8" s="20">
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="27">
+      <c r="A9" s="20">
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="28">
+      <c r="A10" s="21">
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="79" t="s">
-        <v>219</v>
+        <v>64</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="29">
+      <c r="A11" s="22">
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="29">
+      <c r="A12" s="22">
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="30">
+      <c r="A13" s="23">
         <v>11</v>
       </c>
       <c r="B13" s="4">
         <v>11</v>
       </c>
-      <c r="C13" s="79" t="s">
-        <v>80</v>
+      <c r="C13" s="71" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="30">
+      <c r="A14" s="23">
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="31">
+      <c r="A15" s="24">
         <v>13</v>
       </c>
-      <c r="B15" s="79" t="s">
-        <v>83</v>
+      <c r="B15" s="71" t="s">
+        <v>72</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="31">
+      <c r="A16" s="24">
         <v>14</v>
       </c>
-      <c r="B16" s="79" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="79" t="s">
-        <v>86</v>
+      <c r="B16" s="71" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="71" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="33">
+      <c r="A17" s="26">
         <v>15</v>
       </c>
-      <c r="B17" s="79">
+      <c r="B17" s="71">
         <v>5</v>
       </c>
       <c r="C17" s="4"/>
@@ -4383,587 +4646,587 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="B1" s="62" t="s">
+      <c r="A1" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="54" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="15">
+        <v>0</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="56">
+        <v>1</v>
+      </c>
+      <c r="B3" s="57" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="57" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="56">
+        <v>1</v>
+      </c>
+      <c r="B4" s="57" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="56">
+        <v>1</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="D5" s="57" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="62" t="s">
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="58">
+        <v>2</v>
+      </c>
+      <c r="B6" s="43" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="22">
-        <v>0</v>
-      </c>
-      <c r="B2" s="63" t="s">
+      <c r="C6" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="64">
-        <v>1</v>
-      </c>
-      <c r="B3" s="65" t="s">
+      <c r="D6" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="65" t="s">
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="58">
+        <v>2</v>
+      </c>
+      <c r="B7" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="65" t="s">
+      <c r="C7" s="43" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="64">
-        <v>1</v>
-      </c>
-      <c r="B4" s="65" t="s">
+      <c r="D7" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="65" t="s">
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="58">
+        <v>2</v>
+      </c>
+      <c r="B8" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="C8" s="43" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="64">
-        <v>1</v>
-      </c>
-      <c r="B5" s="65" t="s">
+      <c r="D8" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="65" t="s">
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="59">
+        <v>3</v>
+      </c>
+      <c r="B9" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="65" t="s">
+      <c r="C9" s="60" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="66">
-        <v>2</v>
-      </c>
-      <c r="B6" s="51" t="s">
+      <c r="D9" s="60" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="51" t="s">
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="59">
+        <v>3</v>
+      </c>
+      <c r="B10" s="60" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="C10" s="60" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="66">
-        <v>2</v>
-      </c>
-      <c r="B7" s="51" t="s">
+      <c r="D10" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="51" t="s">
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="59">
+        <v>3</v>
+      </c>
+      <c r="B11" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="C11" s="60" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="66">
-        <v>2</v>
-      </c>
-      <c r="B8" s="51" t="s">
+      <c r="D11" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="51" t="s">
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="61">
+        <v>4</v>
+      </c>
+      <c r="B12" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="51" t="s">
+      <c r="C12" s="62" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="67">
-        <v>3</v>
-      </c>
-      <c r="B9" s="68" t="s">
+      <c r="D12" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="C9" s="68" t="s">
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="61">
+        <v>4</v>
+      </c>
+      <c r="B13" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="D9" s="68" t="s">
+      <c r="C13" s="62" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="67">
-        <v>3</v>
-      </c>
-      <c r="B10" s="68" t="s">
+      <c r="D13" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="68" t="s">
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="61">
+        <v>4</v>
+      </c>
+      <c r="B14" s="62" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="68" t="s">
+      <c r="C14" s="62" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="67">
-        <v>3</v>
-      </c>
-      <c r="B11" s="68" t="s">
+      <c r="D14" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="68" t="s">
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="59">
+        <v>5</v>
+      </c>
+      <c r="B15" s="60" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="68" t="s">
+      <c r="C15" s="60" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="69">
-        <v>4</v>
-      </c>
-      <c r="B12" s="70" t="s">
+      <c r="D15" s="60" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="70" t="s">
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="59">
+        <v>5</v>
+      </c>
+      <c r="B16" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="70" t="s">
+      <c r="C16" s="60" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="69">
-        <v>4</v>
-      </c>
-      <c r="B13" s="70" t="s">
+      <c r="D16" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="70" t="s">
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="61">
+        <v>6</v>
+      </c>
+      <c r="B17" s="62" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="C17" s="62" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="69">
-        <v>4</v>
-      </c>
-      <c r="B14" s="70" t="s">
+      <c r="D17" s="62" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="70" t="s">
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="61">
+        <v>6</v>
+      </c>
+      <c r="B18" s="62" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="70" t="s">
+      <c r="C18" s="62" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="67">
-        <v>5</v>
-      </c>
-      <c r="B15" s="68" t="s">
+      <c r="D18" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="68" t="s">
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="61">
+        <v>6</v>
+      </c>
+      <c r="B19" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="D15" s="68" t="s">
+      <c r="C19" s="62" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="67">
-        <v>5</v>
-      </c>
-      <c r="B16" s="68" t="s">
+      <c r="D19" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="68" t="s">
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="27">
+        <v>7</v>
+      </c>
+      <c r="B20" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="D16" s="68" t="s">
+      <c r="C20" s="63" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="69">
-        <v>6</v>
-      </c>
-      <c r="B17" s="70" t="s">
+      <c r="D20" s="63" t="s">
         <v>133</v>
       </c>
-      <c r="C17" s="70" t="s">
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="64">
+        <v>8</v>
+      </c>
+      <c r="B21" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="D17" s="70" t="s">
+      <c r="C21" s="65" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="69">
-        <v>6</v>
-      </c>
-      <c r="B18" s="70" t="s">
+      <c r="D21" s="65" t="s">
         <v>136</v>
       </c>
-      <c r="C18" s="70" t="s">
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="64">
+        <v>8</v>
+      </c>
+      <c r="B22" s="65" t="s">
         <v>137</v>
       </c>
-      <c r="D18" s="70" t="s">
+      <c r="C22" s="65" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="69">
-        <v>6</v>
-      </c>
-      <c r="B19" s="70" t="s">
+      <c r="D22" s="65" t="s">
         <v>139</v>
       </c>
-      <c r="C19" s="70" t="s">
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="27">
+        <v>9</v>
+      </c>
+      <c r="B23" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="D19" s="70" t="s">
+      <c r="C23" s="63" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="34">
-        <v>7</v>
-      </c>
-      <c r="B20" s="71" t="s">
+      <c r="D23" s="63" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="71" t="s">
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="27">
+        <v>9</v>
+      </c>
+      <c r="B24" s="63" t="s">
         <v>143</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="C24" s="63" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="72">
-        <v>8</v>
-      </c>
-      <c r="B21" s="73" t="s">
+      <c r="D24" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="73" t="s">
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="27">
+        <v>9</v>
+      </c>
+      <c r="B25" s="63" t="s">
         <v>146</v>
       </c>
-      <c r="D21" s="73" t="s">
+      <c r="C25" s="63" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="72">
-        <v>8</v>
-      </c>
-      <c r="B22" s="73" t="s">
+      <c r="D25" s="63" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="73" t="s">
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="27">
+        <v>9</v>
+      </c>
+      <c r="B26" s="63" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="73" t="s">
+      <c r="C26" s="63" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="34">
-        <v>9</v>
-      </c>
-      <c r="B23" s="71" t="s">
+      <c r="D26" s="63" t="s">
         <v>151</v>
       </c>
-      <c r="C23" s="71" t="s">
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="64">
+        <v>10</v>
+      </c>
+      <c r="B27" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="D23" s="71" t="s">
+      <c r="C27" s="65" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="34">
-        <v>9</v>
-      </c>
-      <c r="B24" s="71" t="s">
+      <c r="D27" s="65" t="s">
         <v>154</v>
       </c>
-      <c r="C24" s="71" t="s">
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="64">
+        <v>10</v>
+      </c>
+      <c r="B28" s="65" t="s">
         <v>155</v>
       </c>
-      <c r="D24" s="71" t="s">
+      <c r="C28" s="65" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="34">
-        <v>9</v>
-      </c>
-      <c r="B25" s="71" t="s">
+      <c r="D28" s="65" t="s">
         <v>157</v>
       </c>
-      <c r="C25" s="71" t="s">
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="64">
+        <v>10</v>
+      </c>
+      <c r="B29" s="65" t="s">
         <v>158</v>
       </c>
-      <c r="D25" s="71" t="s">
+      <c r="C29" s="65" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="34">
-        <v>9</v>
-      </c>
-      <c r="B26" s="71" t="s">
+      <c r="D29" s="65" t="s">
         <v>160</v>
       </c>
-      <c r="C26" s="71" t="s">
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="64">
+        <v>10</v>
+      </c>
+      <c r="B30" s="65" t="s">
         <v>161</v>
       </c>
-      <c r="D26" s="71" t="s">
+      <c r="C30" s="65" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="72">
+      <c r="D30" s="65" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="64">
         <v>10</v>
       </c>
-      <c r="B27" s="73" t="s">
-        <v>163</v>
-      </c>
-      <c r="C27" s="73" t="s">
+      <c r="B31" s="65" t="s">
         <v>164</v>
       </c>
-      <c r="D27" s="73" t="s">
+      <c r="C31" s="65" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="72">
+      <c r="D31" s="65" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="64">
         <v>10</v>
       </c>
-      <c r="B28" s="73" t="s">
-        <v>166</v>
-      </c>
-      <c r="C28" s="73" t="s">
+      <c r="B32" s="65" t="s">
         <v>167</v>
       </c>
-      <c r="D28" s="73" t="s">
+      <c r="C32" s="65" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="72">
-        <v>10</v>
-      </c>
-      <c r="B29" s="73" t="s">
+      <c r="D32" s="65" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="66">
+        <v>11</v>
+      </c>
+      <c r="B33" s="67" t="s">
         <v>169</v>
       </c>
-      <c r="C29" s="73" t="s">
+      <c r="C33" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="D29" s="73" t="s">
+      <c r="D33" s="67" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="72">
-        <v>10</v>
-      </c>
-      <c r="B30" s="73" t="s">
+    <row r="34" spans="1:4">
+      <c r="A34" s="68">
+        <v>12</v>
+      </c>
+      <c r="B34" s="69" t="s">
         <v>172</v>
       </c>
-      <c r="C30" s="73" t="s">
+      <c r="C34" s="69" t="s">
         <v>173</v>
       </c>
-      <c r="D30" s="73" t="s">
+      <c r="D34" s="69" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="72">
-        <v>10</v>
-      </c>
-      <c r="B31" s="73" t="s">
+    <row r="35" spans="1:4">
+      <c r="A35" s="68">
+        <v>12</v>
+      </c>
+      <c r="B35" s="69" t="s">
         <v>175</v>
       </c>
-      <c r="C31" s="73" t="s">
+      <c r="C35" s="69" t="s">
         <v>176</v>
       </c>
-      <c r="D31" s="73" t="s">
+      <c r="D35" s="69" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="72">
-        <v>10</v>
-      </c>
-      <c r="B32" s="73" t="s">
+    <row r="36" spans="1:4">
+      <c r="A36" s="66">
+        <v>13</v>
+      </c>
+      <c r="B36" s="67" t="s">
         <v>178</v>
       </c>
-      <c r="C32" s="73" t="s">
+      <c r="C36" s="67" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="73" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="74">
-        <v>11</v>
-      </c>
-      <c r="B33" s="75" t="s">
+      <c r="D36" s="67" t="s">
         <v>180</v>
       </c>
-      <c r="C33" s="75" t="s">
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="66">
+        <v>13</v>
+      </c>
+      <c r="B37" s="67" t="s">
         <v>181</v>
       </c>
-      <c r="D33" s="75" t="s">
+      <c r="C37" s="67" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="76">
-        <v>12</v>
-      </c>
-      <c r="B34" s="77" t="s">
+      <c r="D37" s="67" t="s">
         <v>183</v>
       </c>
-      <c r="C34" s="77" t="s">
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="68">
+        <v>14</v>
+      </c>
+      <c r="B38" s="69" t="s">
         <v>184</v>
       </c>
-      <c r="D34" s="77" t="s">
+      <c r="C38" s="69" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="76">
-        <v>12</v>
-      </c>
-      <c r="B35" s="77" t="s">
+      <c r="D38" s="69" t="s">
         <v>186</v>
       </c>
-      <c r="C35" s="77" t="s">
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="68">
+        <v>14</v>
+      </c>
+      <c r="B39" s="69" t="s">
         <v>187</v>
       </c>
-      <c r="D35" s="77" t="s">
+      <c r="C39" s="69" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="74">
-        <v>13</v>
-      </c>
-      <c r="B36" s="75" t="s">
+      <c r="D39" s="69" t="s">
         <v>189</v>
       </c>
-      <c r="C36" s="75" t="s">
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="68">
+        <v>14</v>
+      </c>
+      <c r="B40" s="69" t="s">
         <v>190</v>
       </c>
-      <c r="D36" s="75" t="s">
+      <c r="C40" s="69" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="74">
-        <v>13</v>
-      </c>
-      <c r="B37" s="75" t="s">
+      <c r="D40" s="69" t="s">
         <v>192</v>
       </c>
-      <c r="C37" s="75" t="s">
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="28">
+        <v>15</v>
+      </c>
+      <c r="B41" s="70" t="s">
         <v>193</v>
       </c>
-      <c r="D37" s="75" t="s">
+      <c r="C41" s="70" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="76">
-        <v>14</v>
-      </c>
-      <c r="B38" s="77" t="s">
+      <c r="D41" s="70" t="s">
         <v>195</v>
       </c>
-      <c r="C38" s="77" t="s">
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="28">
+        <v>15</v>
+      </c>
+      <c r="B42" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="D38" s="77" t="s">
+      <c r="C42" s="70" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="76">
-        <v>14</v>
-      </c>
-      <c r="B39" s="77" t="s">
+      <c r="D42" s="70" t="s">
         <v>198</v>
-      </c>
-      <c r="C39" s="77" t="s">
-        <v>199</v>
-      </c>
-      <c r="D39" s="77" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="76">
-        <v>14</v>
-      </c>
-      <c r="B40" s="77" t="s">
-        <v>201</v>
-      </c>
-      <c r="C40" s="77" t="s">
-        <v>202</v>
-      </c>
-      <c r="D40" s="77" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="35">
-        <v>15</v>
-      </c>
-      <c r="B41" s="78" t="s">
-        <v>204</v>
-      </c>
-      <c r="C41" s="78" t="s">
-        <v>205</v>
-      </c>
-      <c r="D41" s="78" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="35">
-        <v>15</v>
-      </c>
-      <c r="B42" s="78" t="s">
-        <v>207</v>
-      </c>
-      <c r="C42" s="78" t="s">
-        <v>208</v>
-      </c>
-      <c r="D42" s="78" t="s">
-        <v>209</v>
       </c>
     </row>
   </sheetData>
